--- a/outputs/daily/hr_rankings_2026-10-28.xlsx
+++ b/outputs/daily/hr_rankings_2026-10-28.xlsx
@@ -735,24 +735,24 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>691406</t>
+          <t>641343</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Junior Caminero</t>
+          <t>Jake Bauers</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>2026-10-29T00:00:00Z</t>
@@ -765,14 +765,14 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>54.7</v>
+        <v>53.3</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>61.9</v>
+        <v>59.6</v>
       </c>
       <c r="Q2" t="n">
         <v>41.2</v>
@@ -799,13 +799,13 @@
         <v>27.6</v>
       </c>
       <c r="S2" t="n">
-        <v>92.09999999999999</v>
+        <v>95.5</v>
       </c>
       <c r="T2" t="n">
         <v>60</v>
       </c>
       <c r="U2" t="n">
-        <v>37.8</v>
+        <v>16.6</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -866,17 +866,17 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Last 7 games: 6/26, 0 HR</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -886,72 +886,72 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>13.37</t>
+          <t>13.91</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>50.21</t>
+          <t>50.01</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>92.61</t>
+          <t>91.98</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>104.9857</t>
+          <t>102.9654</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.4996</t>
+          <t>0.464</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>0.232</t>
+          <t>0.2167</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>0.3586</t>
+          <t>0.3659</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>79.13</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>83.64</t>
+          <t>69.16</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>44.89</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>23.28</t>
+          <t>30.05</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>0.2549</t>
+          <t>0.2018</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr"/>
@@ -975,12 +975,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>641343</t>
+          <t>694192</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Jake Bauers</t>
+          <t>Jackson Chourio</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1005,14 +1005,14 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>53.3</v>
+        <v>51.6</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>59.6</v>
+        <v>50.1</v>
       </c>
       <c r="Q3" t="n">
         <v>41.2</v>
@@ -1039,13 +1039,13 @@
         <v>27.6</v>
       </c>
       <c r="S3" t="n">
-        <v>95.5</v>
+        <v>88.7</v>
       </c>
       <c r="T3" t="n">
         <v>60</v>
       </c>
       <c r="U3" t="n">
-        <v>16.6</v>
+        <v>63.3</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -1101,22 +1101,22 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 0 HR</t>
+          <t>Contact streak: 9/20 over last 7 games</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1131,67 +1131,67 @@
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>13.91</t>
+          <t>11.52</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>50.01</t>
+          <t>45.59</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>91.98</t>
+          <t>90.91</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>102.9654</t>
+          <t>101.9338</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.464</t>
+          <t>0.4603</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>0.2167</t>
+          <t>0.2007</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>0.3659</t>
+          <t>0.3329</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>74.25</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>69.16</t>
+          <t>44.59</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>31.29</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>30.05</t>
+          <t>29.27</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>0.2018</t>
+          <t>0.1951</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr"/>
@@ -1215,24 +1215,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>694192</t>
+          <t>691406</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Jackson Chourio</t>
+          <t>Junior Caminero</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>2026-10-29T00:00:00Z</t>
@@ -1245,14 +1245,26 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Jacob Misiorowski</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>694819</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L4" t="n">
-        <v>51.6</v>
+        <v>48.3</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1270,22 +1282,22 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>50.1</v>
+        <v>61.9</v>
       </c>
       <c r="Q4" t="n">
-        <v>41.2</v>
+        <v>18.6</v>
       </c>
       <c r="R4" t="n">
         <v>27.6</v>
       </c>
       <c r="S4" t="n">
-        <v>88.7</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U4" t="n">
-        <v>63.3</v>
+        <v>37.8</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
@@ -1299,7 +1311,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1324,7 +1336,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr"/>
@@ -1341,12 +1353,12 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1356,90 +1368,114 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Contact streak: 9/20 over last 7 games</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>11.52</t>
+          <t>13.37</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>45.59</t>
+          <t>50.21</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>90.91</t>
+          <t>92.61</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>101.9338</t>
+          <t>104.9857</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.4603</t>
+          <t>0.4996</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.2007</t>
+          <t>0.232</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.3329</t>
+          <t>0.3586</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>74.25</t>
+          <t>79.13</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>44.59</t>
+          <t>83.64</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>31.29</t>
+          <t>44.89</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>29.27</t>
+          <t>23.28</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.1951</t>
-        </is>
-      </c>
-      <c r="BA4" t="inlineStr"/>
-      <c r="BB4" t="inlineStr"/>
-      <c r="BC4" t="inlineStr"/>
-      <c r="BD4" t="inlineStr"/>
-      <c r="BE4" t="inlineStr"/>
-      <c r="BF4" t="inlineStr"/>
+          <t>0.2549</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>4.89</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>34.56</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>87.74</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>0.2817</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>0.0996</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>25.57</t>
+        </is>
+      </c>
       <c r="BG4" t="inlineStr"/>
       <c r="BH4" t="inlineStr"/>
       <c r="BI4" t="inlineStr">
@@ -1455,24 +1491,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>666018</t>
+          <t>661388</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jonathan Aranda</t>
+          <t>William Contreras</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>2026-10-29T00:00:00Z</t>
@@ -1485,14 +1521,14 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>50.4</v>
+        <v>47</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1506,11 +1542,11 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>48.9</v>
+        <v>39.5</v>
       </c>
       <c r="Q5" t="n">
         <v>41.2</v>
@@ -1519,13 +1555,13 @@
         <v>27.6</v>
       </c>
       <c r="S5" t="n">
-        <v>95.5</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T5" t="n">
         <v>60</v>
       </c>
       <c r="U5" t="n">
-        <v>28.9</v>
+        <v>37.8</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -1539,7 +1575,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1581,12 +1617,12 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1596,7 +1632,7 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 1 HR</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1611,67 +1647,67 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>7.87</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>48.55</t>
+          <t>45.42</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>91.67</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>101.2282</t>
+          <t>101.6393</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.4611</t>
+          <t>0.4266</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.196</t>
+          <t>0.1702</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.3547</t>
+          <t>0.3322</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>70.36</t>
+          <t>73.41</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>13.11</t>
+          <t>36.51</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>33.13</t>
+          <t>36.04</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>30.13</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.1639</t>
+          <t>0.1446</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr"/>
@@ -1695,24 +1731,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>661388</t>
+          <t>666018</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>William Contreras</t>
+          <t>Jonathan Aranda</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>2026-10-29T00:00:00Z</t>
@@ -1725,14 +1761,26 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Jacob Misiorowski</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>694819</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L6" t="n">
-        <v>47</v>
+        <v>46.7</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1746,26 +1794,26 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>39.5</v>
+        <v>48.9</v>
       </c>
       <c r="Q6" t="n">
-        <v>41.2</v>
+        <v>18.6</v>
       </c>
       <c r="R6" t="n">
         <v>27.6</v>
       </c>
       <c r="S6" t="n">
-        <v>90.40000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="T6" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U6" t="n">
-        <v>37.8</v>
+        <v>28.9</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -1779,7 +1827,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1804,7 +1852,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr"/>
@@ -1821,12 +1869,12 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1836,12 +1884,12 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Last 7 games: 4/21, 1 HR</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -1851,75 +1899,99 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>7.87</t>
+          <t>10.8</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>45.42</t>
+          <t>48.55</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>91.67</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>101.6393</t>
+          <t>101.2282</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.4266</t>
+          <t>0.4611</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.1702</t>
+          <t>0.196</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3322</t>
+          <t>0.3547</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>73.41</t>
+          <t>70.36</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>36.51</t>
+          <t>13.11</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>36.04</t>
+          <t>33.13</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>30.13</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.1446</t>
-        </is>
-      </c>
-      <c r="BA6" t="inlineStr"/>
-      <c r="BB6" t="inlineStr"/>
-      <c r="BC6" t="inlineStr"/>
-      <c r="BD6" t="inlineStr"/>
-      <c r="BE6" t="inlineStr"/>
-      <c r="BF6" t="inlineStr"/>
+          <t>0.1639</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>4.89</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>34.56</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>87.74</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>0.2817</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>0.0996</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>25.57</t>
+        </is>
+      </c>
       <c r="BG6" t="inlineStr"/>
       <c r="BH6" t="inlineStr"/>
       <c r="BI6" t="inlineStr">
@@ -1935,24 +2007,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>650490</t>
+          <t>592885</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Yandy Diaz</t>
+          <t>Christian Yelich</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>2026-10-29T00:00:00Z</t>
@@ -1965,14 +2037,14 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
-        <v>46.4</v>
+        <v>46.2</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -1990,7 +2062,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>41</v>
+        <v>38.2</v>
       </c>
       <c r="Q7" t="n">
         <v>41.2</v>
@@ -1999,13 +2071,13 @@
         <v>27.6</v>
       </c>
       <c r="S7" t="n">
-        <v>88.7</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T7" t="n">
         <v>60</v>
       </c>
       <c r="U7" t="n">
-        <v>20.9</v>
+        <v>25.3</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -2019,7 +2091,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -2061,22 +2133,22 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/27, 0 HR</t>
+          <t>Last 7 games: 4/24, 1 HR</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -2091,67 +2163,67 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>7.46</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>49.42</t>
+          <t>43.95</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>91.53</t>
+          <t>89.29</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>103.1694</t>
+          <t>100.9775</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.4453</t>
+          <t>0.4012</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.1621</t>
+          <t>0.1674</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3484</t>
+          <t>0.3146</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>73.23</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>32.32</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>23.46</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>19.09</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.1617</t>
+          <t>0.1565</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr"/>
@@ -2175,12 +2247,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>592885</t>
+          <t>668930</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Christian Yelich</t>
+          <t>Brice Turang</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2205,7 +2277,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -2226,11 +2298,11 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>38.2</v>
+        <v>36.6</v>
       </c>
       <c r="Q8" t="n">
         <v>41.2</v>
@@ -2239,13 +2311,13 @@
         <v>27.6</v>
       </c>
       <c r="S8" t="n">
-        <v>92.09999999999999</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T8" t="n">
         <v>60</v>
       </c>
       <c r="U8" t="n">
-        <v>25.3</v>
+        <v>65.2</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -2259,7 +2331,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -2301,22 +2373,22 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -2331,67 +2403,67 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>43.95</t>
+          <t>43.34</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>89.29</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>100.9775</t>
+          <t>100.4264</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.4012</t>
+          <t>0.4283</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.1674</t>
+          <t>0.1712</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3146</t>
+          <t>0.3413</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>70.25</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>32.32</t>
+          <t>13.2</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>19.09</t>
+          <t>23.43</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.1565</t>
+          <t>0.1715</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr"/>
@@ -2415,12 +2487,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>668930</t>
+          <t>669003</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brice Turang</t>
+          <t>Garrett Mitchell</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2445,14 +2517,14 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
-        <v>46.2</v>
+        <v>42.3</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2466,11 +2538,11 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Strong Barrel</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>36.6</v>
+        <v>47.1</v>
       </c>
       <c r="Q9" t="n">
         <v>41.2</v>
@@ -2479,13 +2551,13 @@
         <v>27.6</v>
       </c>
       <c r="S9" t="n">
-        <v>81.90000000000001</v>
+        <v>47.9</v>
       </c>
       <c r="T9" t="n">
         <v>60</v>
       </c>
       <c r="U9" t="n">
-        <v>65.2</v>
+        <v>13.3</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -2499,7 +2571,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -2541,22 +2613,22 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/24, 0 HR</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
@@ -2566,72 +2638,72 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>43.34</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>92.36</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>100.4264</t>
+          <t>103.8477</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.4283</t>
+          <t>0.4152</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.1712</t>
+          <t>0.1589</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3413</t>
+          <t>0.3335</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>70.25</t>
+          <t>77.15</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>77.51</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>32.81</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>23.43</t>
+          <t>16.78</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.1715</t>
+          <t>0.1342</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr"/>
@@ -2655,24 +2727,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>669003</t>
+          <t>650490</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Garrett Mitchell</t>
+          <t>Yandy Diaz</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>2026-10-29T00:00:00Z</t>
@@ -2685,14 +2757,26 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Jacob Misiorowski</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>694819</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L10" t="n">
-        <v>42.3</v>
+        <v>40.1</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -2706,26 +2790,26 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>47.1</v>
+        <v>41</v>
       </c>
       <c r="Q10" t="n">
-        <v>41.2</v>
+        <v>18.6</v>
       </c>
       <c r="R10" t="n">
         <v>27.6</v>
       </c>
       <c r="S10" t="n">
-        <v>47.9</v>
+        <v>88.7</v>
       </c>
       <c r="T10" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U10" t="n">
-        <v>13.3</v>
+        <v>20.9</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -2739,7 +2823,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -2764,7 +2848,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr"/>
@@ -2781,12 +2865,12 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -2796,90 +2880,114 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/24, 0 HR</t>
+          <t>Last 7 games: 7/27, 0 HR</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>7.46</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>49.42</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>92.36</t>
+          <t>91.53</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>103.8477</t>
+          <t>103.1694</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.4152</t>
+          <t>0.4453</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.1589</t>
+          <t>0.1621</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.3335</t>
+          <t>0.3484</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>77.15</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>77.51</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>32.81</t>
+          <t>23.46</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>16.78</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.1342</t>
-        </is>
-      </c>
-      <c r="BA10" t="inlineStr"/>
-      <c r="BB10" t="inlineStr"/>
-      <c r="BC10" t="inlineStr"/>
-      <c r="BD10" t="inlineStr"/>
-      <c r="BE10" t="inlineStr"/>
-      <c r="BF10" t="inlineStr"/>
+          <t>0.1617</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>4.89</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>34.56</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>87.74</t>
+        </is>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>0.2817</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>0.0996</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>25.57</t>
+        </is>
+      </c>
       <c r="BG10" t="inlineStr"/>
       <c r="BH10" t="inlineStr"/>
       <c r="BI10" t="inlineStr">
@@ -2928,11 +3036,23 @@
           <t>7</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Jacob Misiorowski</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>694819</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L11" t="n">
-        <v>42.1</v>
+        <v>35.8</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -2953,7 +3073,7 @@
         <v>43.4</v>
       </c>
       <c r="Q11" t="n">
-        <v>41.2</v>
+        <v>18.6</v>
       </c>
       <c r="R11" t="n">
         <v>27.6</v>
@@ -2962,7 +3082,7 @@
         <v>59.8</v>
       </c>
       <c r="T11" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -3004,7 +3124,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr"/>
@@ -3041,7 +3161,7 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -3114,12 +3234,36 @@
           <t>0.1288</t>
         </is>
       </c>
-      <c r="BA11" t="inlineStr"/>
-      <c r="BB11" t="inlineStr"/>
-      <c r="BC11" t="inlineStr"/>
-      <c r="BD11" t="inlineStr"/>
-      <c r="BE11" t="inlineStr"/>
-      <c r="BF11" t="inlineStr"/>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>4.89</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>34.56</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>87.74</t>
+        </is>
+      </c>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>0.2817</t>
+        </is>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>0.0996</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>25.57</t>
+        </is>
+      </c>
       <c r="BG11" t="inlineStr"/>
       <c r="BH11" t="inlineStr"/>
       <c r="BI11" t="inlineStr">
@@ -3135,24 +3279,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>806198</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Cooper Pratt</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-10-29T00:00:00Z</t>
@@ -3165,14 +3309,14 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
-        <v>37.9</v>
+        <v>32.5</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3186,11 +3330,11 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Hot Hitter/Streak</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>10.6</v>
+        <v>10.5</v>
       </c>
       <c r="Q12" t="n">
         <v>41.2</v>
@@ -3199,13 +3343,13 @@
         <v>27.6</v>
       </c>
       <c r="S12" t="n">
-        <v>81.90000000000001</v>
+        <v>59.8</v>
       </c>
       <c r="T12" t="n">
         <v>60</v>
       </c>
       <c r="U12" t="n">
-        <v>70.59999999999999</v>
+        <v>24.9</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -3219,7 +3363,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -3244,7 +3388,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026 P:</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr"/>
@@ -3261,22 +3405,22 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/21, 0 HR</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
@@ -3291,67 +3435,67 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>97.7063</t>
+          <t>96.5693</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.3262</t>
+          <t>0.362</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.0879</t>
+          <t>0.096</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.2628</t>
+          <t>0.315</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>72.75</t>
+          <t>69.9</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>28.03</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>33.2</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>0.087</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr"/>
@@ -3375,24 +3519,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>689414</t>
+          <t>686217</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Liam Hicks</t>
+          <t>Sal Frelick</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-10-29T00:00:00Z</t>
@@ -3405,14 +3549,14 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
-        <v>35.6</v>
+        <v>32.1</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3426,11 +3570,11 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>7.8</v>
+        <v>5.4</v>
       </c>
       <c r="Q13" t="n">
         <v>41.2</v>
@@ -3439,13 +3583,13 @@
         <v>27.6</v>
       </c>
       <c r="S13" t="n">
-        <v>90.40000000000001</v>
+        <v>71.7</v>
       </c>
       <c r="T13" t="n">
         <v>60</v>
       </c>
       <c r="U13" t="n">
-        <v>19.5</v>
+        <v>17.3</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -3459,7 +3603,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -3501,12 +3645,12 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -3516,7 +3660,7 @@
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 0 HR</t>
+          <t>Last 7 games: 4/17, 0 HR</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
@@ -3531,67 +3675,67 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>27.28</t>
+          <t>26.98</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>85.64</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>96.0847</t>
+          <t>96.2217</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.3556</t>
+          <t>0.3285</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.0997</t>
+          <t>0.0826</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3178</t>
+          <t>0.2864</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>68.03</t>
+          <t>68.24</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>41.33</t>
+          <t>39.46</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.1347</t>
+          <t>0.0974</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr"/>
@@ -3615,24 +3759,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>806198</t>
+          <t>689414</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Cooper Pratt</t>
+          <t>Liam Hicks</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>2026-10-29T00:00:00Z</t>
@@ -3645,14 +3789,26 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Jacob Misiorowski</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>694819</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L14" t="n">
-        <v>32.5</v>
+        <v>32</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -3666,26 +3822,26 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>10.5</v>
+        <v>7.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>41.2</v>
+        <v>18.6</v>
       </c>
       <c r="R14" t="n">
         <v>27.6</v>
       </c>
       <c r="S14" t="n">
-        <v>59.8</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U14" t="n">
-        <v>24.9</v>
+        <v>19.5</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -3699,7 +3855,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -3724,7 +3880,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>H:2026 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr"/>
@@ -3746,7 +3902,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -3756,12 +3912,12 @@
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/21, 0 HR</t>
+          <t>Last 7 games: 6/24, 0 HR</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -3771,75 +3927,99 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>27.28</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>96.5693</t>
+          <t>96.0847</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>0.3556</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>0.0997</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>0.3178</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>69.9</t>
+          <t>68.03</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>33.2</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.087</t>
-        </is>
-      </c>
-      <c r="BA14" t="inlineStr"/>
-      <c r="BB14" t="inlineStr"/>
-      <c r="BC14" t="inlineStr"/>
-      <c r="BD14" t="inlineStr"/>
-      <c r="BE14" t="inlineStr"/>
-      <c r="BF14" t="inlineStr"/>
+          <t>0.1347</t>
+        </is>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>4.89</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>34.56</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>87.74</t>
+        </is>
+      </c>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>0.2817</t>
+        </is>
+      </c>
+      <c r="BE14" t="inlineStr">
+        <is>
+          <t>0.0996</t>
+        </is>
+      </c>
+      <c r="BF14" t="inlineStr">
+        <is>
+          <t>25.57</t>
+        </is>
+      </c>
       <c r="BG14" t="inlineStr"/>
       <c r="BH14" t="inlineStr"/>
       <c r="BI14" t="inlineStr">
@@ -3855,12 +4035,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>680700</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Richie Palacios</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -3885,14 +4065,26 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Jacob Misiorowski</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>694819</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L15" t="n">
-        <v>32.2</v>
+        <v>31.6</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -3906,26 +4098,26 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>15.4</v>
+        <v>10.6</v>
       </c>
       <c r="Q15" t="n">
-        <v>41.2</v>
+        <v>18.6</v>
       </c>
       <c r="R15" t="n">
         <v>27.6</v>
       </c>
       <c r="S15" t="n">
-        <v>47.9</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U15" t="n">
-        <v>19.5</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -3939,7 +4131,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -3964,7 +4156,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr"/>
@@ -3981,27 +4173,27 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/20, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -4011,75 +4203,99 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>87.31</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>97.1084</t>
+          <t>97.7063</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.3655</t>
+          <t>0.3262</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.1018</t>
+          <t>0.0879</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3213</t>
+          <t>0.2628</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>68.91</t>
+          <t>72.75</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>28.03</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>37.09</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>20.98</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.133</t>
-        </is>
-      </c>
-      <c r="BA15" t="inlineStr"/>
-      <c r="BB15" t="inlineStr"/>
-      <c r="BC15" t="inlineStr"/>
-      <c r="BD15" t="inlineStr"/>
-      <c r="BE15" t="inlineStr"/>
-      <c r="BF15" t="inlineStr"/>
+          <t>0.151</t>
+        </is>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>4.89</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>34.56</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>87.74</t>
+        </is>
+      </c>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>0.2817</t>
+        </is>
+      </c>
+      <c r="BE15" t="inlineStr">
+        <is>
+          <t>0.0996</t>
+        </is>
+      </c>
+      <c r="BF15" t="inlineStr">
+        <is>
+          <t>25.57</t>
+        </is>
+      </c>
       <c r="BG15" t="inlineStr"/>
       <c r="BH15" t="inlineStr"/>
       <c r="BI15" t="inlineStr">
@@ -4095,12 +4311,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>686217</t>
+          <t>666152</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sal Frelick</t>
+          <t>David Hamilton</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -4125,14 +4341,14 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="n">
-        <v>32.1</v>
+        <v>29.9</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4150,7 +4366,7 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>5.4</v>
+        <v>11.1</v>
       </c>
       <c r="Q16" t="n">
         <v>41.2</v>
@@ -4159,13 +4375,13 @@
         <v>27.6</v>
       </c>
       <c r="S16" t="n">
-        <v>71.7</v>
+        <v>40.2</v>
       </c>
       <c r="T16" t="n">
         <v>60</v>
       </c>
       <c r="U16" t="n">
-        <v>17.3</v>
+        <v>23.7</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -4179,7 +4395,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -4221,12 +4437,12 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -4236,7 +4452,7 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/17, 0 HR</t>
+          <t>Last 7 games: 5/18, 0 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
@@ -4251,67 +4467,67 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>26.98</t>
+          <t>27.87</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>85.64</t>
+          <t>86.74</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>96.2217</t>
+          <t>96.8019</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.3285</t>
+          <t>0.3169</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.0826</t>
+          <t>0.0967</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.2864</t>
+          <t>0.2712</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>68.24</t>
+          <t>69.66</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>6.59</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>39.46</t>
+          <t>35.88</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>24.48</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.0974</t>
+          <t>0.1042</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr"/>
@@ -4335,12 +4551,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>802415</t>
+          <t>680700</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chandler Simpson</t>
+          <t>Richie Palacios</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -4365,14 +4581,26 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Jacob Misiorowski</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>694819</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L17" t="n">
-        <v>30.3</v>
+        <v>28.6</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -4386,26 +4614,26 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0.2</v>
+        <v>15.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>41.2</v>
+        <v>18.6</v>
       </c>
       <c r="R17" t="n">
         <v>27.6</v>
       </c>
       <c r="S17" t="n">
-        <v>71.7</v>
+        <v>47.9</v>
       </c>
       <c r="T17" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U17" t="n">
-        <v>15.3</v>
+        <v>19.5</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -4419,7 +4647,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -4444,7 +4672,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr"/>
@@ -4461,12 +4689,12 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -4476,12 +4704,12 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 0 HR</t>
+          <t>Last 7 games: 5/20, 0 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -4491,75 +4719,99 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>83.88</t>
+          <t>87.31</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>92.929</t>
+          <t>97.1084</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.3087</t>
+          <t>0.3655</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.0382</t>
+          <t>0.1018</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.2732</t>
+          <t>0.3213</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>68.91</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>37.09</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>12.51</t>
+          <t>20.98</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.05</t>
-        </is>
-      </c>
-      <c r="BA17" t="inlineStr"/>
-      <c r="BB17" t="inlineStr"/>
-      <c r="BC17" t="inlineStr"/>
-      <c r="BD17" t="inlineStr"/>
-      <c r="BE17" t="inlineStr"/>
-      <c r="BF17" t="inlineStr"/>
+          <t>0.133</t>
+        </is>
+      </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>4.89</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>34.56</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>87.74</t>
+        </is>
+      </c>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>0.2817</t>
+        </is>
+      </c>
+      <c r="BE17" t="inlineStr">
+        <is>
+          <t>0.0996</t>
+        </is>
+      </c>
+      <c r="BF17" t="inlineStr">
+        <is>
+          <t>25.57</t>
+        </is>
+      </c>
       <c r="BG17" t="inlineStr"/>
       <c r="BH17" t="inlineStr"/>
       <c r="BI17" t="inlineStr">
@@ -4575,24 +4827,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>666152</t>
+          <t>802415</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>David Hamilton</t>
+          <t>Chandler Simpson</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>2026-10-29T00:00:00Z</t>
@@ -4605,14 +4857,26 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Jacob Misiorowski</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>694819</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L18" t="n">
-        <v>29.9</v>
+        <v>26.7</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -4626,26 +4890,26 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>11.1</v>
+        <v>0.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>41.2</v>
+        <v>18.6</v>
       </c>
       <c r="R18" t="n">
         <v>27.6</v>
       </c>
       <c r="S18" t="n">
-        <v>40.2</v>
+        <v>71.7</v>
       </c>
       <c r="T18" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U18" t="n">
-        <v>23.7</v>
+        <v>15.3</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -4659,7 +4923,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -4684,7 +4948,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr"/>
@@ -4701,12 +4965,12 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -4716,12 +4980,12 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/18, 0 HR</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -4731,75 +4995,99 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>27.87</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>86.74</t>
+          <t>83.88</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>96.8019</t>
+          <t>92.929</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.3169</t>
+          <t>0.3087</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.0967</t>
+          <t>0.0382</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.2712</t>
+          <t>0.2732</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>69.66</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>6.59</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>35.88</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>24.48</t>
+          <t>12.51</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.1042</t>
-        </is>
-      </c>
-      <c r="BA18" t="inlineStr"/>
-      <c r="BB18" t="inlineStr"/>
-      <c r="BC18" t="inlineStr"/>
-      <c r="BD18" t="inlineStr"/>
-      <c r="BE18" t="inlineStr"/>
-      <c r="BF18" t="inlineStr"/>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="BA18" t="inlineStr">
+        <is>
+          <t>4.89</t>
+        </is>
+      </c>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>34.56</t>
+        </is>
+      </c>
+      <c r="BC18" t="inlineStr">
+        <is>
+          <t>87.74</t>
+        </is>
+      </c>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>0.2817</t>
+        </is>
+      </c>
+      <c r="BE18" t="inlineStr">
+        <is>
+          <t>0.0996</t>
+        </is>
+      </c>
+      <c r="BF18" t="inlineStr">
+        <is>
+          <t>25.57</t>
+        </is>
+      </c>
       <c r="BG18" t="inlineStr"/>
       <c r="BH18" t="inlineStr"/>
       <c r="BI18" t="inlineStr">
@@ -4848,11 +5136,23 @@
           <t>9</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Jacob Misiorowski</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>694819</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L19" t="n">
-        <v>29.4</v>
+        <v>23.9</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -4873,7 +5173,7 @@
         <v>5.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>40.2</v>
+        <v>17.3</v>
       </c>
       <c r="R19" t="n">
         <v>27.6</v>
@@ -4924,7 +5224,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr"/>
@@ -4961,7 +5261,7 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -5034,12 +5334,36 @@
           <t>0.0829</t>
         </is>
       </c>
-      <c r="BA19" t="inlineStr"/>
-      <c r="BB19" t="inlineStr"/>
-      <c r="BC19" t="inlineStr"/>
-      <c r="BD19" t="inlineStr"/>
-      <c r="BE19" t="inlineStr"/>
-      <c r="BF19" t="inlineStr"/>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>4.89</t>
+        </is>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>34.56</t>
+        </is>
+      </c>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>87.74</t>
+        </is>
+      </c>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>0.2817</t>
+        </is>
+      </c>
+      <c r="BE19" t="inlineStr">
+        <is>
+          <t>0.0996</t>
+        </is>
+      </c>
+      <c r="BF19" t="inlineStr">
+        <is>
+          <t>25.57</t>
+        </is>
+      </c>
       <c r="BG19" t="inlineStr"/>
       <c r="BH19" t="inlineStr"/>
       <c r="BI19" t="inlineStr">
@@ -5381,24 +5705,24 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>691406</t>
+          <t>641343</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Junior Caminero</t>
+          <t>Jake Bauers</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>2026-10-29T00:00:00Z</t>
@@ -5411,14 +5735,14 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="n">
-        <v>54.7</v>
+        <v>53.3</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -5436,7 +5760,7 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>61.9</v>
+        <v>59.6</v>
       </c>
       <c r="Q2" t="n">
         <v>41.2</v>
@@ -5445,13 +5769,13 @@
         <v>27.6</v>
       </c>
       <c r="S2" t="n">
-        <v>92.09999999999999</v>
+        <v>95.5</v>
       </c>
       <c r="T2" t="n">
         <v>60</v>
       </c>
       <c r="U2" t="n">
-        <v>37.8</v>
+        <v>16.6</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
@@ -5465,7 +5789,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -5512,17 +5836,17 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Last 7 games: 6/26, 0 HR</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -5532,72 +5856,72 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>13.37</t>
+          <t>13.91</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>50.21</t>
+          <t>50.01</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>92.61</t>
+          <t>91.98</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>104.9857</t>
+          <t>102.9654</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.4996</t>
+          <t>0.464</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>0.232</t>
+          <t>0.2167</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>0.3586</t>
+          <t>0.3659</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>79.13</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>83.64</t>
+          <t>69.16</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>44.89</t>
+          <t>39.5</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>23.28</t>
+          <t>30.05</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>20.3</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>0.2549</t>
+          <t>0.2018</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr"/>
@@ -5621,12 +5945,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>641343</t>
+          <t>694192</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Jake Bauers</t>
+          <t>Jackson Chourio</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -5651,14 +5975,14 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="n">
-        <v>53.3</v>
+        <v>51.6</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -5676,7 +6000,7 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>59.6</v>
+        <v>50.1</v>
       </c>
       <c r="Q3" t="n">
         <v>41.2</v>
@@ -5685,13 +6009,13 @@
         <v>27.6</v>
       </c>
       <c r="S3" t="n">
-        <v>95.5</v>
+        <v>88.7</v>
       </c>
       <c r="T3" t="n">
         <v>60</v>
       </c>
       <c r="U3" t="n">
-        <v>16.6</v>
+        <v>63.3</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
@@ -5705,7 +6029,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -5747,22 +6071,22 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/26, 0 HR</t>
+          <t>Contact streak: 9/20 over last 7 games</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -5777,67 +6101,67 @@
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>13.91</t>
+          <t>11.52</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>50.01</t>
+          <t>45.59</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>91.98</t>
+          <t>90.91</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>102.9654</t>
+          <t>101.9338</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.464</t>
+          <t>0.4603</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>0.2167</t>
+          <t>0.2007</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>0.3659</t>
+          <t>0.3329</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>74.25</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>69.16</t>
+          <t>44.59</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>39.5</t>
+          <t>31.29</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>30.05</t>
+          <t>29.27</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>0.2018</t>
+          <t>0.1951</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr"/>
@@ -5861,24 +6185,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>694192</t>
+          <t>691406</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Jackson Chourio</t>
+          <t>Junior Caminero</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>2026-10-29T00:00:00Z</t>
@@ -5891,14 +6215,26 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Jacob Misiorowski</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>694819</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L4" t="n">
-        <v>51.6</v>
+        <v>48.3</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -5916,22 +6252,22 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>50.1</v>
+        <v>61.9</v>
       </c>
       <c r="Q4" t="n">
-        <v>41.2</v>
+        <v>18.6</v>
       </c>
       <c r="R4" t="n">
         <v>27.6</v>
       </c>
       <c r="S4" t="n">
-        <v>88.7</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U4" t="n">
-        <v>63.3</v>
+        <v>37.8</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
@@ -5945,7 +6281,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -5970,7 +6306,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr"/>
@@ -5987,12 +6323,12 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -6002,90 +6338,114 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Contact streak: 9/20 over last 7 games</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>11.52</t>
+          <t>13.37</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>45.59</t>
+          <t>50.21</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>90.91</t>
+          <t>92.61</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>101.9338</t>
+          <t>104.9857</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.4603</t>
+          <t>0.4996</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.2007</t>
+          <t>0.232</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.3329</t>
+          <t>0.3586</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>74.25</t>
+          <t>79.13</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>44.59</t>
+          <t>83.64</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>31.29</t>
+          <t>44.89</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>29.27</t>
+          <t>23.28</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.1951</t>
-        </is>
-      </c>
-      <c r="BA4" t="inlineStr"/>
-      <c r="BB4" t="inlineStr"/>
-      <c r="BC4" t="inlineStr"/>
-      <c r="BD4" t="inlineStr"/>
-      <c r="BE4" t="inlineStr"/>
-      <c r="BF4" t="inlineStr"/>
+          <t>0.2549</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>4.89</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>34.56</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>87.74</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>0.2817</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>0.0996</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>25.57</t>
+        </is>
+      </c>
       <c r="BG4" t="inlineStr"/>
       <c r="BH4" t="inlineStr"/>
       <c r="BI4" t="inlineStr">
@@ -6101,24 +6461,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>666018</t>
+          <t>661388</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jonathan Aranda</t>
+          <t>William Contreras</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>2026-10-29T00:00:00Z</t>
@@ -6131,14 +6491,14 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="n">
-        <v>50.4</v>
+        <v>47</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -6152,11 +6512,11 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>48.9</v>
+        <v>39.5</v>
       </c>
       <c r="Q5" t="n">
         <v>41.2</v>
@@ -6165,13 +6525,13 @@
         <v>27.6</v>
       </c>
       <c r="S5" t="n">
-        <v>95.5</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T5" t="n">
         <v>60</v>
       </c>
       <c r="U5" t="n">
-        <v>28.9</v>
+        <v>37.8</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -6185,7 +6545,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -6227,12 +6587,12 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -6242,7 +6602,7 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 1 HR</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -6257,67 +6617,67 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>7.87</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>48.55</t>
+          <t>45.42</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>91.67</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>101.2282</t>
+          <t>101.6393</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.4611</t>
+          <t>0.4266</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.196</t>
+          <t>0.1702</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.3547</t>
+          <t>0.3322</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>70.36</t>
+          <t>73.41</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>13.11</t>
+          <t>36.51</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>33.13</t>
+          <t>36.04</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>30.13</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.1639</t>
+          <t>0.1446</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr"/>
@@ -6341,24 +6701,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>661388</t>
+          <t>666018</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>William Contreras</t>
+          <t>Jonathan Aranda</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>2026-10-29T00:00:00Z</t>
@@ -6371,14 +6731,26 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Jacob Misiorowski</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>694819</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L6" t="n">
-        <v>47</v>
+        <v>46.7</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -6392,26 +6764,26 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>39.5</v>
+        <v>48.9</v>
       </c>
       <c r="Q6" t="n">
-        <v>41.2</v>
+        <v>18.6</v>
       </c>
       <c r="R6" t="n">
         <v>27.6</v>
       </c>
       <c r="S6" t="n">
-        <v>90.40000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="T6" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U6" t="n">
-        <v>37.8</v>
+        <v>28.9</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -6425,7 +6797,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -6450,7 +6822,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr"/>
@@ -6467,12 +6839,12 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -6482,12 +6854,12 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Last 7 games: 4/21, 1 HR</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -6497,75 +6869,99 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>7.87</t>
+          <t>10.8</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>45.42</t>
+          <t>48.55</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>91.67</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>101.6393</t>
+          <t>101.2282</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.4266</t>
+          <t>0.4611</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.1702</t>
+          <t>0.196</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3322</t>
+          <t>0.3547</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>73.41</t>
+          <t>70.36</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>36.51</t>
+          <t>13.11</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>36.04</t>
+          <t>33.13</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>30.13</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.1446</t>
-        </is>
-      </c>
-      <c r="BA6" t="inlineStr"/>
-      <c r="BB6" t="inlineStr"/>
-      <c r="BC6" t="inlineStr"/>
-      <c r="BD6" t="inlineStr"/>
-      <c r="BE6" t="inlineStr"/>
-      <c r="BF6" t="inlineStr"/>
+          <t>0.1639</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>4.89</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>34.56</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>87.74</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>0.2817</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>0.0996</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>25.57</t>
+        </is>
+      </c>
       <c r="BG6" t="inlineStr"/>
       <c r="BH6" t="inlineStr"/>
       <c r="BI6" t="inlineStr">
@@ -6581,24 +6977,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>650490</t>
+          <t>592885</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Yandy Diaz</t>
+          <t>Christian Yelich</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>2026-10-29T00:00:00Z</t>
@@ -6611,14 +7007,14 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
-        <v>46.4</v>
+        <v>46.2</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -6636,7 +7032,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>41</v>
+        <v>38.2</v>
       </c>
       <c r="Q7" t="n">
         <v>41.2</v>
@@ -6645,13 +7041,13 @@
         <v>27.6</v>
       </c>
       <c r="S7" t="n">
-        <v>88.7</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T7" t="n">
         <v>60</v>
       </c>
       <c r="U7" t="n">
-        <v>20.9</v>
+        <v>25.3</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -6665,7 +7061,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -6707,22 +7103,22 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/27, 0 HR</t>
+          <t>Last 7 games: 4/24, 1 HR</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -6737,67 +7133,67 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>7.46</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>49.42</t>
+          <t>43.95</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>91.53</t>
+          <t>89.29</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>103.1694</t>
+          <t>100.9775</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.4453</t>
+          <t>0.4012</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.1621</t>
+          <t>0.1674</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3484</t>
+          <t>0.3146</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>73.5</t>
+          <t>73.23</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>32.32</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>23.46</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>19.65</t>
+          <t>19.09</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>22.9</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.1617</t>
+          <t>0.1565</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr"/>
@@ -6821,12 +7217,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>592885</t>
+          <t>668930</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Christian Yelich</t>
+          <t>Brice Turang</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -6851,7 +7247,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -6872,11 +7268,11 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>38.2</v>
+        <v>36.6</v>
       </c>
       <c r="Q8" t="n">
         <v>41.2</v>
@@ -6885,13 +7281,13 @@
         <v>27.6</v>
       </c>
       <c r="S8" t="n">
-        <v>92.09999999999999</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T8" t="n">
         <v>60</v>
       </c>
       <c r="U8" t="n">
-        <v>25.3</v>
+        <v>65.2</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -6905,7 +7301,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -6947,22 +7343,22 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -6977,67 +7373,67 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>43.95</t>
+          <t>43.34</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>89.29</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>100.9775</t>
+          <t>100.4264</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.4012</t>
+          <t>0.4283</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.1674</t>
+          <t>0.1712</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3146</t>
+          <t>0.3413</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>70.25</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>32.32</t>
+          <t>13.2</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>19.09</t>
+          <t>23.43</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.1565</t>
+          <t>0.1715</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr"/>
@@ -7061,12 +7457,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>668930</t>
+          <t>669003</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brice Turang</t>
+          <t>Garrett Mitchell</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -7091,14 +7487,14 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
-        <v>46.2</v>
+        <v>42.3</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -7112,11 +7508,11 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Strong Barrel</t>
         </is>
       </c>
       <c r="P9" t="n">
-        <v>36.6</v>
+        <v>47.1</v>
       </c>
       <c r="Q9" t="n">
         <v>41.2</v>
@@ -7125,13 +7521,13 @@
         <v>27.6</v>
       </c>
       <c r="S9" t="n">
-        <v>81.90000000000001</v>
+        <v>47.9</v>
       </c>
       <c r="T9" t="n">
         <v>60</v>
       </c>
       <c r="U9" t="n">
-        <v>65.2</v>
+        <v>13.3</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -7145,7 +7541,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -7187,22 +7583,22 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/24, 0 HR</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
@@ -7212,72 +7608,72 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>10.2</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>43.34</t>
+          <t>49.55</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>92.36</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>100.4264</t>
+          <t>103.8477</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.4283</t>
+          <t>0.4152</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.1712</t>
+          <t>0.1589</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>0.3413</t>
+          <t>0.3335</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>70.25</t>
+          <t>77.15</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>77.51</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>32.81</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>23.43</t>
+          <t>16.78</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.1715</t>
+          <t>0.1342</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr"/>
@@ -7301,24 +7697,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>669003</t>
+          <t>650490</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Garrett Mitchell</t>
+          <t>Yandy Diaz</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>2026-10-29T00:00:00Z</t>
@@ -7331,14 +7727,26 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Jacob Misiorowski</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>694819</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L10" t="n">
-        <v>42.3</v>
+        <v>40.1</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -7352,26 +7760,26 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>47.1</v>
+        <v>41</v>
       </c>
       <c r="Q10" t="n">
-        <v>41.2</v>
+        <v>18.6</v>
       </c>
       <c r="R10" t="n">
         <v>27.6</v>
       </c>
       <c r="S10" t="n">
-        <v>47.9</v>
+        <v>88.7</v>
       </c>
       <c r="T10" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U10" t="n">
-        <v>13.3</v>
+        <v>20.9</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -7385,7 +7793,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -7410,7 +7818,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr"/>
@@ -7427,12 +7835,12 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -7442,90 +7850,114 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/24, 0 HR</t>
+          <t>Last 7 games: 7/27, 0 HR</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>10.2</t>
+          <t>7.46</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>49.55</t>
+          <t>49.42</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>92.36</t>
+          <t>91.53</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>103.8477</t>
+          <t>103.1694</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.4152</t>
+          <t>0.4453</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.1589</t>
+          <t>0.1621</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>0.3335</t>
+          <t>0.3484</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>77.15</t>
+          <t>73.5</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>77.51</t>
+          <t>37.3</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>32.81</t>
+          <t>23.46</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>16.78</t>
+          <t>19.65</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>22.9</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>0.1342</t>
-        </is>
-      </c>
-      <c r="BA10" t="inlineStr"/>
-      <c r="BB10" t="inlineStr"/>
-      <c r="BC10" t="inlineStr"/>
-      <c r="BD10" t="inlineStr"/>
-      <c r="BE10" t="inlineStr"/>
-      <c r="BF10" t="inlineStr"/>
+          <t>0.1617</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>4.89</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>34.56</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>87.74</t>
+        </is>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>0.2817</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>0.0996</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>25.57</t>
+        </is>
+      </c>
       <c r="BG10" t="inlineStr"/>
       <c r="BH10" t="inlineStr"/>
       <c r="BI10" t="inlineStr">
@@ -7574,11 +8006,23 @@
           <t>7</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Jacob Misiorowski</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>694819</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L11" t="n">
-        <v>42.1</v>
+        <v>35.8</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -7599,7 +8043,7 @@
         <v>43.4</v>
       </c>
       <c r="Q11" t="n">
-        <v>41.2</v>
+        <v>18.6</v>
       </c>
       <c r="R11" t="n">
         <v>27.6</v>
@@ -7608,7 +8052,7 @@
         <v>59.8</v>
       </c>
       <c r="T11" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -7650,7 +8094,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr"/>
@@ -7687,7 +8131,7 @@
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -7760,12 +8204,36 @@
           <t>0.1288</t>
         </is>
       </c>
-      <c r="BA11" t="inlineStr"/>
-      <c r="BB11" t="inlineStr"/>
-      <c r="BC11" t="inlineStr"/>
-      <c r="BD11" t="inlineStr"/>
-      <c r="BE11" t="inlineStr"/>
-      <c r="BF11" t="inlineStr"/>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>4.89</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>34.56</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>87.74</t>
+        </is>
+      </c>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>0.2817</t>
+        </is>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>0.0996</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>25.57</t>
+        </is>
+      </c>
       <c r="BG11" t="inlineStr"/>
       <c r="BH11" t="inlineStr"/>
       <c r="BI11" t="inlineStr">
@@ -7781,24 +8249,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>806198</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Cooper Pratt</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-10-29T00:00:00Z</t>
@@ -7811,14 +8279,14 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="n">
-        <v>37.9</v>
+        <v>32.5</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -7832,11 +8300,11 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Hot Hitter/Streak</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>10.6</v>
+        <v>10.5</v>
       </c>
       <c r="Q12" t="n">
         <v>41.2</v>
@@ -7845,13 +8313,13 @@
         <v>27.6</v>
       </c>
       <c r="S12" t="n">
-        <v>81.90000000000001</v>
+        <v>59.8</v>
       </c>
       <c r="T12" t="n">
         <v>60</v>
       </c>
       <c r="U12" t="n">
-        <v>70.59999999999999</v>
+        <v>24.9</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -7865,7 +8333,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -7890,7 +8358,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026 P:</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr"/>
@@ -7907,22 +8375,22 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/21, 0 HR</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
@@ -7937,67 +8405,67 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>97.7063</t>
+          <t>96.5693</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.3262</t>
+          <t>0.362</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.0879</t>
+          <t>0.096</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.2628</t>
+          <t>0.315</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>72.75</t>
+          <t>69.9</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>28.03</t>
+          <t>8.6</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>33.2</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>0.087</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr"/>
@@ -8021,24 +8489,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>689414</t>
+          <t>686217</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Liam Hicks</t>
+          <t>Sal Frelick</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-10-29T00:00:00Z</t>
@@ -8051,14 +8519,14 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="n">
-        <v>35.6</v>
+        <v>32.1</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -8072,11 +8540,11 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>7.8</v>
+        <v>5.4</v>
       </c>
       <c r="Q13" t="n">
         <v>41.2</v>
@@ -8085,13 +8553,13 @@
         <v>27.6</v>
       </c>
       <c r="S13" t="n">
-        <v>90.40000000000001</v>
+        <v>71.7</v>
       </c>
       <c r="T13" t="n">
         <v>60</v>
       </c>
       <c r="U13" t="n">
-        <v>19.5</v>
+        <v>17.3</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -8105,7 +8573,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -8147,12 +8615,12 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -8162,7 +8630,7 @@
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 0 HR</t>
+          <t>Last 7 games: 4/17, 0 HR</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
@@ -8177,67 +8645,67 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>27.28</t>
+          <t>26.98</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>85.64</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>96.0847</t>
+          <t>96.2217</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.3556</t>
+          <t>0.3285</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.0997</t>
+          <t>0.0826</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3178</t>
+          <t>0.2864</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>68.03</t>
+          <t>68.24</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>41.33</t>
+          <t>39.46</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.1347</t>
+          <t>0.0974</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr"/>
@@ -8261,24 +8729,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>806198</t>
+          <t>689414</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Cooper Pratt</t>
+          <t>Liam Hicks</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>2026-10-29T00:00:00Z</t>
@@ -8291,14 +8759,26 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Jacob Misiorowski</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>694819</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L14" t="n">
-        <v>32.5</v>
+        <v>32</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -8312,26 +8792,26 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>10.5</v>
+        <v>7.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>41.2</v>
+        <v>18.6</v>
       </c>
       <c r="R14" t="n">
         <v>27.6</v>
       </c>
       <c r="S14" t="n">
-        <v>59.8</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U14" t="n">
-        <v>24.9</v>
+        <v>19.5</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -8345,7 +8825,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -8370,7 +8850,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>H:2026 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD14" t="inlineStr"/>
@@ -8392,7 +8872,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
@@ -8402,12 +8882,12 @@
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/21, 0 HR</t>
+          <t>Last 7 games: 6/24, 0 HR</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -8417,75 +8897,99 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>27.28</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>96.5693</t>
+          <t>96.0847</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>0.3556</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>0.0997</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>0.3178</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>69.9</t>
+          <t>68.03</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>33.2</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.087</t>
-        </is>
-      </c>
-      <c r="BA14" t="inlineStr"/>
-      <c r="BB14" t="inlineStr"/>
-      <c r="BC14" t="inlineStr"/>
-      <c r="BD14" t="inlineStr"/>
-      <c r="BE14" t="inlineStr"/>
-      <c r="BF14" t="inlineStr"/>
+          <t>0.1347</t>
+        </is>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>4.89</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>34.56</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>87.74</t>
+        </is>
+      </c>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>0.2817</t>
+        </is>
+      </c>
+      <c r="BE14" t="inlineStr">
+        <is>
+          <t>0.0996</t>
+        </is>
+      </c>
+      <c r="BF14" t="inlineStr">
+        <is>
+          <t>25.57</t>
+        </is>
+      </c>
       <c r="BG14" t="inlineStr"/>
       <c r="BH14" t="inlineStr"/>
       <c r="BI14" t="inlineStr">
@@ -8501,12 +9005,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>680700</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Richie Palacios</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -8531,14 +9035,26 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Jacob Misiorowski</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>694819</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L15" t="n">
-        <v>32.2</v>
+        <v>31.6</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -8552,26 +9068,26 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>15.4</v>
+        <v>10.6</v>
       </c>
       <c r="Q15" t="n">
-        <v>41.2</v>
+        <v>18.6</v>
       </c>
       <c r="R15" t="n">
         <v>27.6</v>
       </c>
       <c r="S15" t="n">
-        <v>47.9</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U15" t="n">
-        <v>19.5</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -8585,7 +9101,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -8610,7 +9126,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD15" t="inlineStr"/>
@@ -8627,27 +9143,27 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/20, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -8657,75 +9173,99 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>87.31</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>97.1084</t>
+          <t>97.7063</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.3655</t>
+          <t>0.3262</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.1018</t>
+          <t>0.0879</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3213</t>
+          <t>0.2628</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>68.91</t>
+          <t>72.75</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>28.03</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>37.09</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>20.98</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.133</t>
-        </is>
-      </c>
-      <c r="BA15" t="inlineStr"/>
-      <c r="BB15" t="inlineStr"/>
-      <c r="BC15" t="inlineStr"/>
-      <c r="BD15" t="inlineStr"/>
-      <c r="BE15" t="inlineStr"/>
-      <c r="BF15" t="inlineStr"/>
+          <t>0.151</t>
+        </is>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>4.89</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>34.56</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>87.74</t>
+        </is>
+      </c>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>0.2817</t>
+        </is>
+      </c>
+      <c r="BE15" t="inlineStr">
+        <is>
+          <t>0.0996</t>
+        </is>
+      </c>
+      <c r="BF15" t="inlineStr">
+        <is>
+          <t>25.57</t>
+        </is>
+      </c>
       <c r="BG15" t="inlineStr"/>
       <c r="BH15" t="inlineStr"/>
       <c r="BI15" t="inlineStr">
@@ -8741,12 +9281,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>686217</t>
+          <t>666152</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sal Frelick</t>
+          <t>David Hamilton</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -8771,14 +9311,14 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="n">
-        <v>32.1</v>
+        <v>29.9</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -8796,7 +9336,7 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>5.4</v>
+        <v>11.1</v>
       </c>
       <c r="Q16" t="n">
         <v>41.2</v>
@@ -8805,13 +9345,13 @@
         <v>27.6</v>
       </c>
       <c r="S16" t="n">
-        <v>71.7</v>
+        <v>40.2</v>
       </c>
       <c r="T16" t="n">
         <v>60</v>
       </c>
       <c r="U16" t="n">
-        <v>17.3</v>
+        <v>23.7</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -8825,7 +9365,7 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
@@ -8867,12 +9407,12 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -8882,7 +9422,7 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/17, 0 HR</t>
+          <t>Last 7 games: 5/18, 0 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
@@ -8897,67 +9437,67 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>26.98</t>
+          <t>27.87</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>85.64</t>
+          <t>86.74</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>96.2217</t>
+          <t>96.8019</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.3285</t>
+          <t>0.3169</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.0826</t>
+          <t>0.0967</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.2864</t>
+          <t>0.2712</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>68.24</t>
+          <t>69.66</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>6.59</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>39.46</t>
+          <t>35.88</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>24.48</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.0974</t>
+          <t>0.1042</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr"/>
@@ -8981,12 +9521,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>802415</t>
+          <t>680700</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chandler Simpson</t>
+          <t>Richie Palacios</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -9011,14 +9551,26 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Jacob Misiorowski</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>694819</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L17" t="n">
-        <v>30.3</v>
+        <v>28.6</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -9032,26 +9584,26 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0.2</v>
+        <v>15.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>41.2</v>
+        <v>18.6</v>
       </c>
       <c r="R17" t="n">
         <v>27.6</v>
       </c>
       <c r="S17" t="n">
-        <v>71.7</v>
+        <v>47.9</v>
       </c>
       <c r="T17" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U17" t="n">
-        <v>15.3</v>
+        <v>19.5</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -9065,7 +9617,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -9090,7 +9642,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr"/>
@@ -9107,12 +9659,12 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -9122,12 +9674,12 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 0 HR</t>
+          <t>Last 7 games: 5/20, 0 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -9137,75 +9689,99 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>83.88</t>
+          <t>87.31</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>92.929</t>
+          <t>97.1084</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.3087</t>
+          <t>0.3655</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.0382</t>
+          <t>0.1018</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.2732</t>
+          <t>0.3213</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>68.91</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>37.09</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>12.51</t>
+          <t>20.98</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.05</t>
-        </is>
-      </c>
-      <c r="BA17" t="inlineStr"/>
-      <c r="BB17" t="inlineStr"/>
-      <c r="BC17" t="inlineStr"/>
-      <c r="BD17" t="inlineStr"/>
-      <c r="BE17" t="inlineStr"/>
-      <c r="BF17" t="inlineStr"/>
+          <t>0.133</t>
+        </is>
+      </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>4.89</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>34.56</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>87.74</t>
+        </is>
+      </c>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>0.2817</t>
+        </is>
+      </c>
+      <c r="BE17" t="inlineStr">
+        <is>
+          <t>0.0996</t>
+        </is>
+      </c>
+      <c r="BF17" t="inlineStr">
+        <is>
+          <t>25.57</t>
+        </is>
+      </c>
       <c r="BG17" t="inlineStr"/>
       <c r="BH17" t="inlineStr"/>
       <c r="BI17" t="inlineStr">
@@ -9221,24 +9797,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>666152</t>
+          <t>802415</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>David Hamilton</t>
+          <t>Chandler Simpson</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>2026-10-29T00:00:00Z</t>
@@ -9251,14 +9827,26 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Jacob Misiorowski</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>694819</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L18" t="n">
-        <v>29.9</v>
+        <v>26.7</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -9272,26 +9860,26 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>11.1</v>
+        <v>0.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>41.2</v>
+        <v>18.6</v>
       </c>
       <c r="R18" t="n">
         <v>27.6</v>
       </c>
       <c r="S18" t="n">
-        <v>40.2</v>
+        <v>71.7</v>
       </c>
       <c r="T18" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U18" t="n">
-        <v>23.7</v>
+        <v>15.3</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -9305,7 +9893,7 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
@@ -9330,7 +9918,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD18" t="inlineStr"/>
@@ -9347,12 +9935,12 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -9362,12 +9950,12 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/18, 0 HR</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -9377,75 +9965,99 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>27.87</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>86.74</t>
+          <t>83.88</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>96.8019</t>
+          <t>92.929</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.3169</t>
+          <t>0.3087</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.0967</t>
+          <t>0.0382</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.2712</t>
+          <t>0.2732</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>69.66</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>6.59</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>35.88</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>24.48</t>
+          <t>12.51</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.1042</t>
-        </is>
-      </c>
-      <c r="BA18" t="inlineStr"/>
-      <c r="BB18" t="inlineStr"/>
-      <c r="BC18" t="inlineStr"/>
-      <c r="BD18" t="inlineStr"/>
-      <c r="BE18" t="inlineStr"/>
-      <c r="BF18" t="inlineStr"/>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="BA18" t="inlineStr">
+        <is>
+          <t>4.89</t>
+        </is>
+      </c>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>34.56</t>
+        </is>
+      </c>
+      <c r="BC18" t="inlineStr">
+        <is>
+          <t>87.74</t>
+        </is>
+      </c>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>0.2817</t>
+        </is>
+      </c>
+      <c r="BE18" t="inlineStr">
+        <is>
+          <t>0.0996</t>
+        </is>
+      </c>
+      <c r="BF18" t="inlineStr">
+        <is>
+          <t>25.57</t>
+        </is>
+      </c>
       <c r="BG18" t="inlineStr"/>
       <c r="BH18" t="inlineStr"/>
       <c r="BI18" t="inlineStr">
@@ -9494,11 +10106,23 @@
           <t>9</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Jacob Misiorowski</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>694819</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L19" t="n">
-        <v>29.4</v>
+        <v>23.9</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -9519,7 +10143,7 @@
         <v>5.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>40.2</v>
+        <v>17.3</v>
       </c>
       <c r="R19" t="n">
         <v>27.6</v>
@@ -9570,7 +10194,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD19" t="inlineStr"/>
@@ -9607,7 +10231,7 @@
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>switch hitter; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>switch hitter; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
@@ -9680,12 +10304,36 @@
           <t>0.0829</t>
         </is>
       </c>
-      <c r="BA19" t="inlineStr"/>
-      <c r="BB19" t="inlineStr"/>
-      <c r="BC19" t="inlineStr"/>
-      <c r="BD19" t="inlineStr"/>
-      <c r="BE19" t="inlineStr"/>
-      <c r="BF19" t="inlineStr"/>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>4.89</t>
+        </is>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>34.56</t>
+        </is>
+      </c>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>87.74</t>
+        </is>
+      </c>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>0.2817</t>
+        </is>
+      </c>
+      <c r="BE19" t="inlineStr">
+        <is>
+          <t>0.0996</t>
+        </is>
+      </c>
+      <c r="BF19" t="inlineStr">
+        <is>
+          <t>25.57</t>
+        </is>
+      </c>
       <c r="BG19" t="inlineStr"/>
       <c r="BH19" t="inlineStr"/>
       <c r="BI19" t="inlineStr">

--- a/outputs/daily/hr_rankings_2026-10-28.xlsx
+++ b/outputs/daily/hr_rankings_2026-10-28.xlsx
@@ -814,7 +814,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -2198,12 +2198,12 @@
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>73.16</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>32.32</t>
+          <t>32.25</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
@@ -2326,7 +2326,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -2517,14 +2517,14 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
-        <v>42.3</v>
+        <v>45.7</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
         <v>27.6</v>
       </c>
       <c r="S9" t="n">
-        <v>47.9</v>
+        <v>71.7</v>
       </c>
       <c r="T9" t="n">
         <v>60</v>
@@ -2566,12 +2566,12 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>77.51</t>
+          <t>77.58</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -2935,7 +2935,7 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>37.37</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
@@ -3003,12 +3003,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>668723</t>
+          <t>683748</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ryan Vilade</t>
+          <t>Victor Mesa</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -3052,7 +3052,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>35.8</v>
+        <v>39.6</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3066,11 +3066,11 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>43.4</v>
+        <v>43.6</v>
       </c>
       <c r="Q11" t="n">
         <v>18.6</v>
@@ -3079,13 +3079,13 @@
         <v>27.6</v>
       </c>
       <c r="S11" t="n">
-        <v>59.8</v>
+        <v>47.9</v>
       </c>
       <c r="T11" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>54.9</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -3094,12 +3094,12 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -3141,27 +3141,27 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/21, 0 HR</t>
+          <t>Contact streak: 8/22 over last 7 games</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -3171,67 +3171,67 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>50.43</t>
+          <t>42.41</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>91.42</t>
+          <t>89.91</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>102.6273</t>
+          <t>100.2811</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.3949</t>
+          <t>0.4339</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.1562</t>
+          <t>0.1893</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3174</t>
+          <t>0.3305</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>75.91</t>
+          <t>73.58</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>58.98</t>
+          <t>32.32</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>40.38</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>33.35</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.1288</t>
+          <t>0.2134</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -3475,7 +3475,7 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
@@ -3519,24 +3519,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>686217</t>
+          <t>689414</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sal Frelick</t>
+          <t>Liam Hicks</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-10-29T00:00:00Z</t>
@@ -3549,14 +3549,26 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Jacob Misiorowski</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>694819</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L13" t="n">
-        <v>32.1</v>
+        <v>32</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3570,26 +3582,26 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>5.4</v>
+        <v>7.8</v>
       </c>
       <c r="Q13" t="n">
-        <v>41.2</v>
+        <v>18.6</v>
       </c>
       <c r="R13" t="n">
         <v>27.6</v>
       </c>
       <c r="S13" t="n">
-        <v>71.7</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U13" t="n">
-        <v>17.3</v>
+        <v>19.5</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -3598,24 +3610,24 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
+      <c r="Z13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -3628,7 +3640,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr"/>
@@ -3645,12 +3657,12 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -3660,12 +3672,12 @@
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/17, 0 HR</t>
+          <t>Last 7 games: 6/24, 0 HR</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -3675,75 +3687,99 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>26.98</t>
+          <t>27.28</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>85.64</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>96.2217</t>
+          <t>96.0847</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.3285</t>
+          <t>0.3556</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.0826</t>
+          <t>0.0997</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.2864</t>
+          <t>0.3178</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>68.24</t>
+          <t>68.03</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>39.46</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.0974</t>
-        </is>
-      </c>
-      <c r="BA13" t="inlineStr"/>
-      <c r="BB13" t="inlineStr"/>
-      <c r="BC13" t="inlineStr"/>
-      <c r="BD13" t="inlineStr"/>
-      <c r="BE13" t="inlineStr"/>
-      <c r="BF13" t="inlineStr"/>
+          <t>0.1347</t>
+        </is>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>4.89</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>34.56</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>87.74</t>
+        </is>
+      </c>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>0.2817</t>
+        </is>
+      </c>
+      <c r="BE13" t="inlineStr">
+        <is>
+          <t>0.0996</t>
+        </is>
+      </c>
+      <c r="BF13" t="inlineStr">
+        <is>
+          <t>25.57</t>
+        </is>
+      </c>
       <c r="BG13" t="inlineStr"/>
       <c r="BH13" t="inlineStr"/>
       <c r="BI13" t="inlineStr">
@@ -3759,12 +3795,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>689414</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Liam Hicks</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -3789,7 +3825,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -3808,7 +3844,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>32</v>
+        <v>31.6</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -3822,11 +3858,11 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>7.8</v>
+        <v>10.6</v>
       </c>
       <c r="Q14" t="n">
         <v>18.6</v>
@@ -3835,13 +3871,13 @@
         <v>27.6</v>
       </c>
       <c r="S14" t="n">
-        <v>90.40000000000001</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U14" t="n">
-        <v>19.5</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -3850,12 +3886,12 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -3897,27 +3933,27 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -3927,67 +3963,67 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>27.28</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>96.0847</t>
+          <t>97.7063</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.3556</t>
+          <t>0.3262</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.0997</t>
+          <t>0.0879</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.3178</t>
+          <t>0.2628</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>68.03</t>
+          <t>72.75</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>28.1</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>41.33</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.1347</t>
+          <t>0.151</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
@@ -4035,12 +4071,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>680700</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Richie Palacios</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -4065,7 +4101,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -4084,7 +4120,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>31.6</v>
+        <v>30.2</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4098,11 +4134,11 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>10.6</v>
+        <v>15.4</v>
       </c>
       <c r="Q15" t="n">
         <v>18.6</v>
@@ -4111,13 +4147,13 @@
         <v>27.6</v>
       </c>
       <c r="S15" t="n">
-        <v>81.90000000000001</v>
+        <v>59.8</v>
       </c>
       <c r="T15" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U15" t="n">
-        <v>70.59999999999999</v>
+        <v>19.5</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -4126,12 +4162,12 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -4173,27 +4209,27 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/20, 0 HR</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -4203,67 +4239,67 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>87.31</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>97.7063</t>
+          <t>97.1084</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.3262</t>
+          <t>0.3655</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.0879</t>
+          <t>0.1018</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.2628</t>
+          <t>0.3213</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>72.75</t>
+          <t>68.91</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>28.03</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>37.09</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>20.98</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>0.133</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
@@ -4390,7 +4426,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -4507,7 +4543,7 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>6.59</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
@@ -4551,24 +4587,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>680700</t>
+          <t>686217</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Richie Palacios</t>
+          <t>Sal Frelick</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>2026-10-29T00:00:00Z</t>
@@ -4584,23 +4620,11 @@
           <t>8</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Jacob Misiorowski</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>694819</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="n">
-        <v>28.6</v>
+        <v>28.8</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -4614,14 +4638,14 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>15.4</v>
+        <v>5.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>18.6</v>
+        <v>41.2</v>
       </c>
       <c r="R17" t="n">
         <v>27.6</v>
@@ -4630,10 +4654,10 @@
         <v>47.9</v>
       </c>
       <c r="T17" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="U17" t="n">
-        <v>19.5</v>
+        <v>17.3</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -4642,24 +4666,24 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
+      <c r="Z17" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -4672,7 +4696,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr"/>
@@ -4689,12 +4713,12 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -4704,12 +4728,12 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/20, 0 HR</t>
+          <t>Last 7 games: 4/17, 0 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -4719,99 +4743,75 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>26.98</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>87.31</t>
+          <t>85.64</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>97.1084</t>
+          <t>96.2217</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.3655</t>
+          <t>0.3285</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.1018</t>
+          <t>0.0826</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.3213</t>
+          <t>0.2864</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>68.91</t>
+          <t>68.24</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>37.09</t>
+          <t>39.46</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>20.98</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.133</t>
-        </is>
-      </c>
-      <c r="BA17" t="inlineStr">
-        <is>
-          <t>4.89</t>
-        </is>
-      </c>
-      <c r="BB17" t="inlineStr">
-        <is>
-          <t>34.56</t>
-        </is>
-      </c>
-      <c r="BC17" t="inlineStr">
-        <is>
-          <t>87.74</t>
-        </is>
-      </c>
-      <c r="BD17" t="inlineStr">
-        <is>
-          <t>0.2817</t>
-        </is>
-      </c>
-      <c r="BE17" t="inlineStr">
-        <is>
-          <t>0.0996</t>
-        </is>
-      </c>
-      <c r="BF17" t="inlineStr">
-        <is>
-          <t>25.57</t>
-        </is>
-      </c>
+          <t>0.0974</t>
+        </is>
+      </c>
+      <c r="BA17" t="inlineStr"/>
+      <c r="BB17" t="inlineStr"/>
+      <c r="BC17" t="inlineStr"/>
+      <c r="BD17" t="inlineStr"/>
+      <c r="BE17" t="inlineStr"/>
+      <c r="BF17" t="inlineStr"/>
       <c r="BG17" t="inlineStr"/>
       <c r="BH17" t="inlineStr"/>
       <c r="BI17" t="inlineStr">
@@ -4918,7 +4918,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -5784,7 +5784,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -6024,7 +6024,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -6540,7 +6540,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -6792,7 +6792,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -7056,7 +7056,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -7168,12 +7168,12 @@
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>73.23</t>
+          <t>73.16</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>32.32</t>
+          <t>32.25</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
@@ -7296,7 +7296,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -7487,14 +7487,14 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="n">
-        <v>42.3</v>
+        <v>45.7</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -7521,7 +7521,7 @@
         <v>27.6</v>
       </c>
       <c r="S9" t="n">
-        <v>47.9</v>
+        <v>71.7</v>
       </c>
       <c r="T9" t="n">
         <v>60</v>
@@ -7536,12 +7536,12 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -7653,7 +7653,7 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>77.51</t>
+          <t>77.58</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
@@ -7788,7 +7788,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -7905,7 +7905,7 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>37.37</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
@@ -7973,12 +7973,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>668723</t>
+          <t>683748</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ryan Vilade</t>
+          <t>Victor Mesa</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -8003,7 +8003,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -8022,7 +8022,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>35.8</v>
+        <v>39.6</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -8036,11 +8036,11 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>43.4</v>
+        <v>43.6</v>
       </c>
       <c r="Q11" t="n">
         <v>18.6</v>
@@ -8049,13 +8049,13 @@
         <v>27.6</v>
       </c>
       <c r="S11" t="n">
-        <v>59.8</v>
+        <v>47.9</v>
       </c>
       <c r="T11" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>54.9</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -8064,12 +8064,12 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -8111,27 +8111,27 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Last 7 games: 2/21, 0 HR</t>
+          <t>Contact streak: 8/22 over last 7 games</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -8141,67 +8141,67 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>8.72</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>50.43</t>
+          <t>42.41</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>91.42</t>
+          <t>89.91</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>102.6273</t>
+          <t>100.2811</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.3949</t>
+          <t>0.4339</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.1562</t>
+          <t>0.1893</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3174</t>
+          <t>0.3305</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>75.91</t>
+          <t>73.58</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>58.98</t>
+          <t>32.32</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>24.71</t>
+          <t>40.38</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>23.91</t>
+          <t>33.35</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>10.1</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.1288</t>
+          <t>0.2134</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
@@ -8328,7 +8328,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -8445,7 +8445,7 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>8.6</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
@@ -8489,24 +8489,24 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>686217</t>
+          <t>689414</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sal Frelick</t>
+          <t>Liam Hicks</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>2026-10-29T00:00:00Z</t>
@@ -8519,14 +8519,26 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Jacob Misiorowski</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>694819</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L13" t="n">
-        <v>32.1</v>
+        <v>32</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -8540,26 +8552,26 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>5.4</v>
+        <v>7.8</v>
       </c>
       <c r="Q13" t="n">
-        <v>41.2</v>
+        <v>18.6</v>
       </c>
       <c r="R13" t="n">
         <v>27.6</v>
       </c>
       <c r="S13" t="n">
-        <v>71.7</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U13" t="n">
-        <v>17.3</v>
+        <v>19.5</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -8568,24 +8580,24 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
+      <c r="Z13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -8598,7 +8610,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD13" t="inlineStr"/>
@@ -8615,12 +8627,12 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
@@ -8630,12 +8642,12 @@
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/17, 0 HR</t>
+          <t>Last 7 games: 6/24, 0 HR</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -8645,75 +8657,99 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>26.98</t>
+          <t>27.28</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>85.64</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>96.2217</t>
+          <t>96.0847</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.3285</t>
+          <t>0.3556</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.0826</t>
+          <t>0.0997</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.2864</t>
+          <t>0.3178</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>68.24</t>
+          <t>68.03</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>39.46</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.0974</t>
-        </is>
-      </c>
-      <c r="BA13" t="inlineStr"/>
-      <c r="BB13" t="inlineStr"/>
-      <c r="BC13" t="inlineStr"/>
-      <c r="BD13" t="inlineStr"/>
-      <c r="BE13" t="inlineStr"/>
-      <c r="BF13" t="inlineStr"/>
+          <t>0.1347</t>
+        </is>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>4.89</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>34.56</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>87.74</t>
+        </is>
+      </c>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>0.2817</t>
+        </is>
+      </c>
+      <c r="BE13" t="inlineStr">
+        <is>
+          <t>0.0996</t>
+        </is>
+      </c>
+      <c r="BF13" t="inlineStr">
+        <is>
+          <t>25.57</t>
+        </is>
+      </c>
       <c r="BG13" t="inlineStr"/>
       <c r="BH13" t="inlineStr"/>
       <c r="BI13" t="inlineStr">
@@ -8729,12 +8765,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>689414</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Liam Hicks</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -8759,7 +8795,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -8778,7 +8814,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>32</v>
+        <v>31.6</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -8792,11 +8828,11 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>7.8</v>
+        <v>10.6</v>
       </c>
       <c r="Q14" t="n">
         <v>18.6</v>
@@ -8805,13 +8841,13 @@
         <v>27.6</v>
       </c>
       <c r="S14" t="n">
-        <v>90.40000000000001</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U14" t="n">
-        <v>19.5</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -8820,12 +8856,12 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -8867,27 +8903,27 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -8897,67 +8933,67 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>27.28</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>96.0847</t>
+          <t>97.7063</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.3556</t>
+          <t>0.3262</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.0997</t>
+          <t>0.0879</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.3178</t>
+          <t>0.2628</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>68.03</t>
+          <t>72.75</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>28.1</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>41.33</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.1347</t>
+          <t>0.151</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
@@ -9005,12 +9041,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>680700</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Richie Palacios</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -9035,7 +9071,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -9054,7 +9090,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>31.6</v>
+        <v>30.2</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -9068,11 +9104,11 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>10.6</v>
+        <v>15.4</v>
       </c>
       <c r="Q15" t="n">
         <v>18.6</v>
@@ -9081,13 +9117,13 @@
         <v>27.6</v>
       </c>
       <c r="S15" t="n">
-        <v>81.90000000000001</v>
+        <v>59.8</v>
       </c>
       <c r="T15" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U15" t="n">
-        <v>70.59999999999999</v>
+        <v>19.5</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -9096,12 +9132,12 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -9143,27 +9179,27 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 5/20, 0 HR</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -9173,67 +9209,67 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>87.31</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>97.7063</t>
+          <t>97.1084</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.3262</t>
+          <t>0.3655</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.0879</t>
+          <t>0.1018</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.2628</t>
+          <t>0.3213</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>72.75</t>
+          <t>68.91</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>28.03</t>
+          <t>3.94</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>37.09</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>20.98</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>7.3</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>0.133</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
@@ -9360,7 +9396,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -9477,7 +9513,7 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>6.59</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
@@ -9521,24 +9557,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>680700</t>
+          <t>686217</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Richie Palacios</t>
+          <t>Sal Frelick</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>2026-10-29T00:00:00Z</t>
@@ -9554,23 +9590,11 @@
           <t>8</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Jacob Misiorowski</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>694819</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>R</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="n">
-        <v>28.6</v>
+        <v>28.8</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -9584,14 +9608,14 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Projected Lineup</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>15.4</v>
+        <v>5.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>18.6</v>
+        <v>41.2</v>
       </c>
       <c r="R17" t="n">
         <v>27.6</v>
@@ -9600,10 +9624,10 @@
         <v>47.9</v>
       </c>
       <c r="T17" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="U17" t="n">
-        <v>19.5</v>
+        <v>17.3</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -9612,24 +9636,24 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
+      <c r="Z17" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>RotoWire projected lineup; MLB probable pitchers</t>
@@ -9642,7 +9666,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr"/>
@@ -9659,12 +9683,12 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -9674,12 +9698,12 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/20, 0 HR</t>
+          <t>Last 7 games: 4/17, 0 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -9689,99 +9713,75 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>26.98</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>87.31</t>
+          <t>85.64</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>97.1084</t>
+          <t>96.2217</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.3655</t>
+          <t>0.3285</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.1018</t>
+          <t>0.0826</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.3213</t>
+          <t>0.2864</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>68.91</t>
+          <t>68.24</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>37.09</t>
+          <t>39.46</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>20.98</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.133</t>
-        </is>
-      </c>
-      <c r="BA17" t="inlineStr">
-        <is>
-          <t>4.89</t>
-        </is>
-      </c>
-      <c r="BB17" t="inlineStr">
-        <is>
-          <t>34.56</t>
-        </is>
-      </c>
-      <c r="BC17" t="inlineStr">
-        <is>
-          <t>87.74</t>
-        </is>
-      </c>
-      <c r="BD17" t="inlineStr">
-        <is>
-          <t>0.2817</t>
-        </is>
-      </c>
-      <c r="BE17" t="inlineStr">
-        <is>
-          <t>0.0996</t>
-        </is>
-      </c>
-      <c r="BF17" t="inlineStr">
-        <is>
-          <t>25.57</t>
-        </is>
-      </c>
+          <t>0.0974</t>
+        </is>
+      </c>
+      <c r="BA17" t="inlineStr"/>
+      <c r="BB17" t="inlineStr"/>
+      <c r="BC17" t="inlineStr"/>
+      <c r="BD17" t="inlineStr"/>
+      <c r="BE17" t="inlineStr"/>
+      <c r="BF17" t="inlineStr"/>
       <c r="BG17" t="inlineStr"/>
       <c r="BH17" t="inlineStr"/>
       <c r="BI17" t="inlineStr">
@@ -9888,7 +9888,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -10164,7 +10164,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">

--- a/outputs/daily/hr_rankings_2026-10-28.xlsx
+++ b/outputs/daily/hr_rankings_2026-10-28.xlsx
@@ -768,11 +768,23 @@
           <t>2</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Drew Rasmussen</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>656876</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L2" t="n">
-        <v>53.3</v>
+        <v>52</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -786,14 +798,14 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P2" t="n">
         <v>59.6</v>
       </c>
       <c r="Q2" t="n">
-        <v>41.2</v>
+        <v>28.5</v>
       </c>
       <c r="R2" t="n">
         <v>27.6</v>
@@ -802,7 +814,7 @@
         <v>95.5</v>
       </c>
       <c r="T2" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U2" t="n">
         <v>16.6</v>
@@ -844,7 +856,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr"/>
@@ -881,7 +893,7 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
@@ -954,12 +966,36 @@
           <t>0.2018</t>
         </is>
       </c>
-      <c r="BA2" t="inlineStr"/>
-      <c r="BB2" t="inlineStr"/>
-      <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="inlineStr"/>
-      <c r="BE2" t="inlineStr"/>
-      <c r="BF2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>6.02</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>36.65</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>88.92</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>0.3526</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>0.1222</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>23.38</t>
+        </is>
+      </c>
       <c r="BG2" t="inlineStr"/>
       <c r="BH2" t="inlineStr"/>
       <c r="BI2" t="inlineStr">
@@ -975,24 +1011,24 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>694192</t>
+          <t>691406</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Jackson Chourio</t>
+          <t>Junior Caminero</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>2026-10-29T00:00:00Z</t>
@@ -1005,14 +1041,26 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Jacob Misiorowski</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>694819</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L3" t="n">
-        <v>51.6</v>
+        <v>48.3</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1030,22 +1078,22 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>50.1</v>
+        <v>61.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>41.2</v>
+        <v>18.6</v>
       </c>
       <c r="R3" t="n">
         <v>27.6</v>
       </c>
       <c r="S3" t="n">
-        <v>88.7</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U3" t="n">
-        <v>63.3</v>
+        <v>37.8</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
@@ -1059,7 +1107,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -1084,7 +1132,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr"/>
@@ -1101,12 +1149,12 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -1116,90 +1164,114 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Contact streak: 9/20 over last 7 games</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>11.52</t>
+          <t>13.37</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>45.59</t>
+          <t>50.21</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>90.91</t>
+          <t>92.61</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>101.9338</t>
+          <t>104.9857</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.4603</t>
+          <t>0.4996</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>0.2007</t>
+          <t>0.232</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>0.3329</t>
+          <t>0.3586</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>74.25</t>
+          <t>79.13</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>44.59</t>
+          <t>83.64</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>31.29</t>
+          <t>44.89</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>29.27</t>
+          <t>23.28</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>0.1951</t>
-        </is>
-      </c>
-      <c r="BA3" t="inlineStr"/>
-      <c r="BB3" t="inlineStr"/>
-      <c r="BC3" t="inlineStr"/>
-      <c r="BD3" t="inlineStr"/>
-      <c r="BE3" t="inlineStr"/>
-      <c r="BF3" t="inlineStr"/>
+          <t>0.2549</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>4.89</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>34.56</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>87.74</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>0.2817</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>0.0996</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>25.57</t>
+        </is>
+      </c>
       <c r="BG3" t="inlineStr"/>
       <c r="BH3" t="inlineStr"/>
       <c r="BI3" t="inlineStr">
@@ -1215,24 +1287,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>691406</t>
+          <t>694192</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Junior Caminero</t>
+          <t>Jackson Chourio</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>2026-10-29T00:00:00Z</t>
@@ -1245,17 +1317,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Jacob Misiorowski</t>
+          <t>Drew Rasmussen</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>694819</t>
+          <t>656876</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1264,7 +1336,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>48.3</v>
+        <v>47.6</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1282,22 +1354,22 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>61.9</v>
+        <v>50.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>18.6</v>
+        <v>28.5</v>
       </c>
       <c r="R4" t="n">
         <v>27.6</v>
       </c>
       <c r="S4" t="n">
-        <v>92.09999999999999</v>
+        <v>88.7</v>
       </c>
       <c r="T4" t="n">
         <v>50</v>
       </c>
       <c r="U4" t="n">
-        <v>37.8</v>
+        <v>63.3</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
@@ -1311,7 +1383,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1353,12 +1425,12 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -1368,112 +1440,112 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Contact streak: 9/20 over last 7 games</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>13.37</t>
+          <t>11.52</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>50.21</t>
+          <t>45.59</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>92.61</t>
+          <t>90.91</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>104.9857</t>
+          <t>101.9338</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.4996</t>
+          <t>0.4603</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.232</t>
+          <t>0.2007</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.3586</t>
+          <t>0.3329</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>79.13</t>
+          <t>74.25</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>83.64</t>
+          <t>44.59</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>44.89</t>
+          <t>31.29</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>23.28</t>
+          <t>29.27</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.2549</t>
+          <t>0.1951</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>87.74</t>
+          <t>88.92</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>0.2817</t>
+          <t>0.3526</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>0.0996</t>
+          <t>0.1222</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>25.57</t>
+          <t>23.38</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr"/>
@@ -1491,24 +1563,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>661388</t>
+          <t>666018</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>William Contreras</t>
+          <t>Jonathan Aranda</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>2026-10-29T00:00:00Z</t>
@@ -1521,14 +1593,26 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Jacob Misiorowski</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>694819</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L5" t="n">
-        <v>47</v>
+        <v>46.7</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1542,26 +1626,26 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>39.5</v>
+        <v>48.9</v>
       </c>
       <c r="Q5" t="n">
-        <v>41.2</v>
+        <v>18.6</v>
       </c>
       <c r="R5" t="n">
         <v>27.6</v>
       </c>
       <c r="S5" t="n">
-        <v>90.40000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="T5" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U5" t="n">
-        <v>37.8</v>
+        <v>28.9</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -1575,7 +1659,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1600,7 +1684,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr"/>
@@ -1617,12 +1701,12 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -1632,12 +1716,12 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Last 7 games: 4/21, 1 HR</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -1647,75 +1731,99 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>7.87</t>
+          <t>10.8</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>45.42</t>
+          <t>48.55</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>91.67</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>101.6393</t>
+          <t>101.2282</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.4266</t>
+          <t>0.4611</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.1702</t>
+          <t>0.196</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.3322</t>
+          <t>0.3547</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>73.41</t>
+          <t>70.36</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>36.51</t>
+          <t>13.11</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>36.04</t>
+          <t>33.13</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>30.13</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.1446</t>
-        </is>
-      </c>
-      <c r="BA5" t="inlineStr"/>
-      <c r="BB5" t="inlineStr"/>
-      <c r="BC5" t="inlineStr"/>
-      <c r="BD5" t="inlineStr"/>
-      <c r="BE5" t="inlineStr"/>
-      <c r="BF5" t="inlineStr"/>
+          <t>0.1639</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>4.89</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>34.56</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>87.74</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>0.2817</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>0.0996</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>25.57</t>
+        </is>
+      </c>
       <c r="BG5" t="inlineStr"/>
       <c r="BH5" t="inlineStr"/>
       <c r="BI5" t="inlineStr">
@@ -1731,24 +1839,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>666018</t>
+          <t>592885</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jonathan Aranda</t>
+          <t>Christian Yelich</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>2026-10-29T00:00:00Z</t>
@@ -1761,17 +1869,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Jacob Misiorowski</t>
+          <t>Drew Rasmussen</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>694819</t>
+          <t>656876</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1780,7 +1888,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>46.7</v>
+        <v>45</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1794,26 +1902,26 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>48.9</v>
+        <v>38.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>18.6</v>
+        <v>28.5</v>
       </c>
       <c r="R6" t="n">
         <v>27.6</v>
       </c>
       <c r="S6" t="n">
-        <v>95.5</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T6" t="n">
         <v>80</v>
       </c>
       <c r="U6" t="n">
-        <v>28.9</v>
+        <v>25.3</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -1827,7 +1935,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1874,7 +1982,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -1884,12 +1992,12 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 1 HR</t>
+          <t>Last 7 games: 4/24, 1 HR</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -1899,97 +2007,97 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>48.55</t>
+          <t>43.95</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>91.67</t>
+          <t>89.29</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>101.2282</t>
+          <t>100.9775</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.4611</t>
+          <t>0.4012</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.196</t>
+          <t>0.1674</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3547</t>
+          <t>0.3146</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>70.36</t>
+          <t>73.16</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>13.11</t>
+          <t>32.25</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>33.13</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>30.13</t>
+          <t>19.09</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.1639</t>
+          <t>0.1565</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>87.74</t>
+          <t>88.92</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>0.2817</t>
+          <t>0.3526</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>0.0996</t>
+          <t>0.1222</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>25.57</t>
+          <t>23.38</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr"/>
@@ -2007,12 +2115,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>592885</t>
+          <t>668930</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Christian Yelich</t>
+          <t>Brice Turang</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -2037,14 +2145,26 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Drew Rasmussen</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>656876</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L7" t="n">
-        <v>46.2</v>
+        <v>45</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2058,26 +2178,26 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>38.2</v>
+        <v>36.6</v>
       </c>
       <c r="Q7" t="n">
-        <v>41.2</v>
+        <v>28.5</v>
       </c>
       <c r="R7" t="n">
         <v>27.6</v>
       </c>
       <c r="S7" t="n">
-        <v>92.09999999999999</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U7" t="n">
-        <v>25.3</v>
+        <v>65.2</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -2091,7 +2211,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -2116,7 +2236,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr"/>
@@ -2133,27 +2253,27 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -2163,75 +2283,99 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>43.95</t>
+          <t>43.34</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>89.29</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>100.9775</t>
+          <t>100.4264</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.4012</t>
+          <t>0.4283</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.1674</t>
+          <t>0.1712</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3146</t>
+          <t>0.3413</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>73.16</t>
+          <t>70.25</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>32.25</t>
+          <t>13.2</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>19.09</t>
+          <t>23.43</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.1565</t>
-        </is>
-      </c>
-      <c r="BA7" t="inlineStr"/>
-      <c r="BB7" t="inlineStr"/>
-      <c r="BC7" t="inlineStr"/>
-      <c r="BD7" t="inlineStr"/>
-      <c r="BE7" t="inlineStr"/>
-      <c r="BF7" t="inlineStr"/>
+          <t>0.1715</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>6.02</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>36.65</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>88.92</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>0.3526</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>0.1222</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>23.38</t>
+        </is>
+      </c>
       <c r="BG7" t="inlineStr"/>
       <c r="BH7" t="inlineStr"/>
       <c r="BI7" t="inlineStr">
@@ -2247,12 +2391,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>668930</t>
+          <t>661388</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brice Turang</t>
+          <t>William Contreras</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2277,14 +2421,26 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Drew Rasmussen</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>656876</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L8" t="n">
-        <v>46.2</v>
+        <v>43.1</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2298,26 +2454,26 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>36.6</v>
+        <v>39.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>41.2</v>
+        <v>28.5</v>
       </c>
       <c r="R8" t="n">
         <v>27.6</v>
       </c>
       <c r="S8" t="n">
-        <v>81.90000000000001</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U8" t="n">
-        <v>65.2</v>
+        <v>37.8</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -2331,7 +2487,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -2356,7 +2512,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr"/>
@@ -2373,27 +2529,27 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
@@ -2403,12 +2559,12 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>7.87</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>43.34</t>
+          <t>45.42</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
@@ -2418,60 +2574,84 @@
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>100.4264</t>
+          <t>101.6393</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.4283</t>
+          <t>0.4266</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.1712</t>
+          <t>0.1702</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3413</t>
+          <t>0.3322</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>70.25</t>
+          <t>73.41</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>36.51</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>36.04</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>23.43</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.1715</t>
-        </is>
-      </c>
-      <c r="BA8" t="inlineStr"/>
-      <c r="BB8" t="inlineStr"/>
-      <c r="BC8" t="inlineStr"/>
-      <c r="BD8" t="inlineStr"/>
-      <c r="BE8" t="inlineStr"/>
-      <c r="BF8" t="inlineStr"/>
+          <t>0.1446</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>6.02</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>36.65</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>88.92</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>0.3526</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>0.1222</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>23.38</t>
+        </is>
+      </c>
       <c r="BG8" t="inlineStr"/>
       <c r="BH8" t="inlineStr"/>
       <c r="BI8" t="inlineStr">
@@ -2517,14 +2697,26 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Drew Rasmussen</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>656876</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L9" t="n">
-        <v>45.7</v>
+        <v>41.1</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2538,23 +2730,23 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
         <v>47.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>41.2</v>
+        <v>28.5</v>
       </c>
       <c r="R9" t="n">
         <v>27.6</v>
       </c>
       <c r="S9" t="n">
-        <v>71.7</v>
+        <v>47.9</v>
       </c>
       <c r="T9" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U9" t="n">
         <v>13.3</v>
@@ -2571,7 +2763,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -2596,7 +2788,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr"/>
@@ -2633,7 +2825,7 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -2706,12 +2898,36 @@
           <t>0.1342</t>
         </is>
       </c>
-      <c r="BA9" t="inlineStr"/>
-      <c r="BB9" t="inlineStr"/>
-      <c r="BC9" t="inlineStr"/>
-      <c r="BD9" t="inlineStr"/>
-      <c r="BE9" t="inlineStr"/>
-      <c r="BF9" t="inlineStr"/>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>6.02</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>36.65</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>88.92</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>0.3526</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>0.1222</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>23.38</t>
+        </is>
+      </c>
       <c r="BG9" t="inlineStr"/>
       <c r="BH9" t="inlineStr"/>
       <c r="BI9" t="inlineStr">
@@ -3279,24 +3495,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>806198</t>
+          <t>689414</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cooper Pratt</t>
+          <t>Liam Hicks</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-10-29T00:00:00Z</t>
@@ -3309,14 +3525,26 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Jacob Misiorowski</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>694819</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L12" t="n">
-        <v>32.5</v>
+        <v>32</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3330,26 +3558,26 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>10.5</v>
+        <v>7.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>41.2</v>
+        <v>18.6</v>
       </c>
       <c r="R12" t="n">
         <v>27.6</v>
       </c>
       <c r="S12" t="n">
-        <v>59.8</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U12" t="n">
-        <v>24.9</v>
+        <v>19.5</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -3363,7 +3591,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -3388,7 +3616,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>H:2026 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr"/>
@@ -3410,7 +3638,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -3420,12 +3648,12 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/21, 0 HR</t>
+          <t>Last 7 games: 6/24, 0 HR</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -3435,75 +3663,99 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>27.28</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>96.5693</t>
+          <t>96.0847</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>0.3556</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>0.0997</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>0.3178</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>69.9</t>
+          <t>68.03</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>33.2</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.087</t>
-        </is>
-      </c>
-      <c r="BA12" t="inlineStr"/>
-      <c r="BB12" t="inlineStr"/>
-      <c r="BC12" t="inlineStr"/>
-      <c r="BD12" t="inlineStr"/>
-      <c r="BE12" t="inlineStr"/>
-      <c r="BF12" t="inlineStr"/>
+          <t>0.1347</t>
+        </is>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>4.89</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>34.56</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>87.74</t>
+        </is>
+      </c>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>0.2817</t>
+        </is>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>0.0996</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>25.57</t>
+        </is>
+      </c>
       <c r="BG12" t="inlineStr"/>
       <c r="BH12" t="inlineStr"/>
       <c r="BI12" t="inlineStr">
@@ -3519,12 +3771,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>689414</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Liam Hicks</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -3549,7 +3801,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -3568,7 +3820,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>32</v>
+        <v>31.6</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3582,11 +3834,11 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>7.8</v>
+        <v>10.6</v>
       </c>
       <c r="Q13" t="n">
         <v>18.6</v>
@@ -3595,13 +3847,13 @@
         <v>27.6</v>
       </c>
       <c r="S13" t="n">
-        <v>90.40000000000001</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U13" t="n">
-        <v>19.5</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -3615,7 +3867,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -3657,27 +3909,27 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -3687,67 +3939,67 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>27.28</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>96.0847</t>
+          <t>97.7063</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.3556</t>
+          <t>0.3262</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.0997</t>
+          <t>0.0879</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3178</t>
+          <t>0.2628</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>68.03</t>
+          <t>72.75</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>28.1</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>41.33</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.1347</t>
+          <t>0.151</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
@@ -3795,24 +4047,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>686217</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Sal Frelick</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>2026-10-29T00:00:00Z</t>
@@ -3825,17 +4077,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Jacob Misiorowski</t>
+          <t>Drew Rasmussen</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>694819</t>
+          <t>656876</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -3844,7 +4096,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>31.6</v>
+        <v>30.9</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -3858,26 +4110,26 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>10.6</v>
+        <v>5.4</v>
       </c>
       <c r="Q14" t="n">
-        <v>18.6</v>
+        <v>28.5</v>
       </c>
       <c r="R14" t="n">
         <v>27.6</v>
       </c>
       <c r="S14" t="n">
-        <v>81.90000000000001</v>
+        <v>71.7</v>
       </c>
       <c r="T14" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U14" t="n">
-        <v>70.59999999999999</v>
+        <v>17.3</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -3891,7 +4143,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -3933,27 +4185,27 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 4/17, 0 HR</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -3963,97 +4215,97 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>26.98</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>85.64</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>97.7063</t>
+          <t>96.2217</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.3262</t>
+          <t>0.3285</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.0879</t>
+          <t>0.0826</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.2628</t>
+          <t>0.2864</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>72.75</t>
+          <t>68.24</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>28.1</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>39.46</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>0.0974</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>87.74</t>
+          <t>88.92</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>0.2817</t>
+          <t>0.3526</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>0.0996</t>
+          <t>0.1222</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>25.57</t>
+          <t>23.38</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr"/>
@@ -4380,11 +4632,23 @@
           <t>9</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Drew Rasmussen</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>656876</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L16" t="n">
-        <v>29.9</v>
+        <v>28.7</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4398,14 +4662,14 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
         <v>11.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>41.2</v>
+        <v>28.5</v>
       </c>
       <c r="R16" t="n">
         <v>27.6</v>
@@ -4414,7 +4678,7 @@
         <v>40.2</v>
       </c>
       <c r="T16" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U16" t="n">
         <v>23.7</v>
@@ -4456,7 +4720,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr"/>
@@ -4493,7 +4757,7 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -4566,12 +4830,36 @@
           <t>0.1042</t>
         </is>
       </c>
-      <c r="BA16" t="inlineStr"/>
-      <c r="BB16" t="inlineStr"/>
-      <c r="BC16" t="inlineStr"/>
-      <c r="BD16" t="inlineStr"/>
-      <c r="BE16" t="inlineStr"/>
-      <c r="BF16" t="inlineStr"/>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>6.02</t>
+        </is>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>36.65</t>
+        </is>
+      </c>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>88.92</t>
+        </is>
+      </c>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>0.3526</t>
+        </is>
+      </c>
+      <c r="BE16" t="inlineStr">
+        <is>
+          <t>0.1222</t>
+        </is>
+      </c>
+      <c r="BF16" t="inlineStr">
+        <is>
+          <t>23.38</t>
+        </is>
+      </c>
       <c r="BG16" t="inlineStr"/>
       <c r="BH16" t="inlineStr"/>
       <c r="BI16" t="inlineStr">
@@ -4587,12 +4875,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>686217</t>
+          <t>806198</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sal Frelick</t>
+          <t>Cooper Pratt</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -4617,14 +4905,26 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Drew Rasmussen</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>656876</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L17" t="n">
-        <v>28.8</v>
+        <v>28.6</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -4642,22 +4942,22 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>5.4</v>
+        <v>10.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>41.2</v>
+        <v>28.5</v>
       </c>
       <c r="R17" t="n">
         <v>27.6</v>
       </c>
       <c r="S17" t="n">
-        <v>47.9</v>
+        <v>59.8</v>
       </c>
       <c r="T17" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U17" t="n">
-        <v>17.3</v>
+        <v>24.9</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -4671,7 +4971,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -4696,7 +4996,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr"/>
@@ -4713,12 +5013,12 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -4728,12 +5028,12 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/17, 0 HR</t>
+          <t>Last 7 games: 6/21, 0 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -4743,75 +5043,99 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>26.98</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>85.64</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>96.2217</t>
+          <t>96.5693</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.3285</t>
+          <t>0.362</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.0826</t>
+          <t>0.096</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.2864</t>
+          <t>0.315</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>68.24</t>
+          <t>69.9</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>39.46</t>
+          <t>33.2</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.0974</t>
-        </is>
-      </c>
-      <c r="BA17" t="inlineStr"/>
-      <c r="BB17" t="inlineStr"/>
-      <c r="BC17" t="inlineStr"/>
-      <c r="BD17" t="inlineStr"/>
-      <c r="BE17" t="inlineStr"/>
-      <c r="BF17" t="inlineStr"/>
+          <t>0.087</t>
+        </is>
+      </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>6.02</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>36.65</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>88.92</t>
+        </is>
+      </c>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>0.3526</t>
+        </is>
+      </c>
+      <c r="BE17" t="inlineStr">
+        <is>
+          <t>0.1222</t>
+        </is>
+      </c>
+      <c r="BF17" t="inlineStr">
+        <is>
+          <t>23.38</t>
+        </is>
+      </c>
       <c r="BG17" t="inlineStr"/>
       <c r="BH17" t="inlineStr"/>
       <c r="BI17" t="inlineStr">
@@ -5738,11 +6062,23 @@
           <t>2</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Drew Rasmussen</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>656876</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L2" t="n">
-        <v>53.3</v>
+        <v>52</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -5756,14 +6092,14 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P2" t="n">
         <v>59.6</v>
       </c>
       <c r="Q2" t="n">
-        <v>41.2</v>
+        <v>28.5</v>
       </c>
       <c r="R2" t="n">
         <v>27.6</v>
@@ -5772,7 +6108,7 @@
         <v>95.5</v>
       </c>
       <c r="T2" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U2" t="n">
         <v>16.6</v>
@@ -5814,7 +6150,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr"/>
@@ -5851,7 +6187,7 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
@@ -5924,12 +6260,36 @@
           <t>0.2018</t>
         </is>
       </c>
-      <c r="BA2" t="inlineStr"/>
-      <c r="BB2" t="inlineStr"/>
-      <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="inlineStr"/>
-      <c r="BE2" t="inlineStr"/>
-      <c r="BF2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>6.02</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>36.65</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>88.92</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>0.3526</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>0.1222</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>23.38</t>
+        </is>
+      </c>
       <c r="BG2" t="inlineStr"/>
       <c r="BH2" t="inlineStr"/>
       <c r="BI2" t="inlineStr">
@@ -5945,24 +6305,24 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>694192</t>
+          <t>691406</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Jackson Chourio</t>
+          <t>Junior Caminero</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>2026-10-29T00:00:00Z</t>
@@ -5975,14 +6335,26 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Jacob Misiorowski</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>694819</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L3" t="n">
-        <v>51.6</v>
+        <v>48.3</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -6000,22 +6372,22 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>50.1</v>
+        <v>61.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>41.2</v>
+        <v>18.6</v>
       </c>
       <c r="R3" t="n">
         <v>27.6</v>
       </c>
       <c r="S3" t="n">
-        <v>88.7</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U3" t="n">
-        <v>63.3</v>
+        <v>37.8</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
@@ -6029,7 +6401,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -6054,7 +6426,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr"/>
@@ -6071,12 +6443,12 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
@@ -6086,90 +6458,114 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Contact streak: 9/20 over last 7 games</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>11.52</t>
+          <t>13.37</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>45.59</t>
+          <t>50.21</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>90.91</t>
+          <t>92.61</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>101.9338</t>
+          <t>104.9857</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.4603</t>
+          <t>0.4996</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>0.2007</t>
+          <t>0.232</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>0.3329</t>
+          <t>0.3586</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>74.25</t>
+          <t>79.13</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>44.59</t>
+          <t>83.64</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>31.29</t>
+          <t>44.89</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>29.27</t>
+          <t>23.28</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>42.9</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>0.1951</t>
-        </is>
-      </c>
-      <c r="BA3" t="inlineStr"/>
-      <c r="BB3" t="inlineStr"/>
-      <c r="BC3" t="inlineStr"/>
-      <c r="BD3" t="inlineStr"/>
-      <c r="BE3" t="inlineStr"/>
-      <c r="BF3" t="inlineStr"/>
+          <t>0.2549</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>4.89</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>34.56</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>87.74</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>0.2817</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>0.0996</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>25.57</t>
+        </is>
+      </c>
       <c r="BG3" t="inlineStr"/>
       <c r="BH3" t="inlineStr"/>
       <c r="BI3" t="inlineStr">
@@ -6185,24 +6581,24 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>691406</t>
+          <t>694192</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Junior Caminero</t>
+          <t>Jackson Chourio</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>2026-10-29T00:00:00Z</t>
@@ -6215,17 +6611,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Jacob Misiorowski</t>
+          <t>Drew Rasmussen</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>694819</t>
+          <t>656876</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -6234,7 +6630,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>48.3</v>
+        <v>47.6</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -6252,22 +6648,22 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>61.9</v>
+        <v>50.1</v>
       </c>
       <c r="Q4" t="n">
-        <v>18.6</v>
+        <v>28.5</v>
       </c>
       <c r="R4" t="n">
         <v>27.6</v>
       </c>
       <c r="S4" t="n">
-        <v>92.09999999999999</v>
+        <v>88.7</v>
       </c>
       <c r="T4" t="n">
         <v>50</v>
       </c>
       <c r="U4" t="n">
-        <v>37.8</v>
+        <v>63.3</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
@@ -6281,7 +6677,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -6323,12 +6719,12 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -6338,112 +6734,112 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Contact streak: 9/20 over last 7 games</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>13.37</t>
+          <t>11.52</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>50.21</t>
+          <t>45.59</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>92.61</t>
+          <t>90.91</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>104.9857</t>
+          <t>101.9338</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.4996</t>
+          <t>0.4603</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.232</t>
+          <t>0.2007</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.3586</t>
+          <t>0.3329</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>79.13</t>
+          <t>74.25</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>83.64</t>
+          <t>44.59</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>44.89</t>
+          <t>31.29</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>23.28</t>
+          <t>29.27</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>23.8</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.2549</t>
+          <t>0.1951</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>87.74</t>
+          <t>88.92</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>0.2817</t>
+          <t>0.3526</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>0.0996</t>
+          <t>0.1222</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>25.57</t>
+          <t>23.38</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr"/>
@@ -6461,24 +6857,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>661388</t>
+          <t>666018</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>William Contreras</t>
+          <t>Jonathan Aranda</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>2026-10-29T00:00:00Z</t>
@@ -6491,14 +6887,26 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Jacob Misiorowski</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>694819</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L5" t="n">
-        <v>47</v>
+        <v>46.7</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -6512,26 +6920,26 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>39.5</v>
+        <v>48.9</v>
       </c>
       <c r="Q5" t="n">
-        <v>41.2</v>
+        <v>18.6</v>
       </c>
       <c r="R5" t="n">
         <v>27.6</v>
       </c>
       <c r="S5" t="n">
-        <v>90.40000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="T5" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U5" t="n">
-        <v>37.8</v>
+        <v>28.9</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -6545,7 +6953,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -6570,7 +6978,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr"/>
@@ -6587,12 +6995,12 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -6602,12 +7010,12 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Last 7 games: 4/21, 1 HR</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
@@ -6617,75 +7025,99 @@
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>7.87</t>
+          <t>10.8</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>45.42</t>
+          <t>48.55</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>90.54</t>
+          <t>91.67</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>101.6393</t>
+          <t>101.2282</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.4266</t>
+          <t>0.4611</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.1702</t>
+          <t>0.196</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.3322</t>
+          <t>0.3547</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>73.41</t>
+          <t>70.36</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>36.51</t>
+          <t>13.11</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>36.04</t>
+          <t>33.13</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>24.43</t>
+          <t>30.13</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>17.7</t>
+          <t>19.6</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.1446</t>
-        </is>
-      </c>
-      <c r="BA5" t="inlineStr"/>
-      <c r="BB5" t="inlineStr"/>
-      <c r="BC5" t="inlineStr"/>
-      <c r="BD5" t="inlineStr"/>
-      <c r="BE5" t="inlineStr"/>
-      <c r="BF5" t="inlineStr"/>
+          <t>0.1639</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>4.89</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>34.56</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>87.74</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>0.2817</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>0.0996</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>25.57</t>
+        </is>
+      </c>
       <c r="BG5" t="inlineStr"/>
       <c r="BH5" t="inlineStr"/>
       <c r="BI5" t="inlineStr">
@@ -6701,24 +7133,24 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>666018</t>
+          <t>592885</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jonathan Aranda</t>
+          <t>Christian Yelich</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>2026-10-29T00:00:00Z</t>
@@ -6731,17 +7163,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Jacob Misiorowski</t>
+          <t>Drew Rasmussen</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>694819</t>
+          <t>656876</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -6750,7 +7182,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>46.7</v>
+        <v>45</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -6764,26 +7196,26 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
-        <v>48.9</v>
+        <v>38.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>18.6</v>
+        <v>28.5</v>
       </c>
       <c r="R6" t="n">
         <v>27.6</v>
       </c>
       <c r="S6" t="n">
-        <v>95.5</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T6" t="n">
         <v>80</v>
       </c>
       <c r="U6" t="n">
-        <v>28.9</v>
+        <v>25.3</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -6797,7 +7229,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -6844,7 +7276,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
@@ -6854,12 +7286,12 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/21, 1 HR</t>
+          <t>Last 7 games: 4/24, 1 HR</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
@@ -6869,97 +7301,97 @@
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>10.8</t>
+          <t>9.81</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>48.55</t>
+          <t>43.95</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>91.67</t>
+          <t>89.29</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>101.2282</t>
+          <t>100.9775</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.4611</t>
+          <t>0.4012</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.196</t>
+          <t>0.1674</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.3547</t>
+          <t>0.3146</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>70.36</t>
+          <t>73.16</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>13.11</t>
+          <t>32.25</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>33.13</t>
+          <t>34.24</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>30.13</t>
+          <t>19.09</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>19.6</t>
+          <t>17.1</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.1639</t>
+          <t>0.1565</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>87.74</t>
+          <t>88.92</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>0.2817</t>
+          <t>0.3526</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>0.0996</t>
+          <t>0.1222</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>25.57</t>
+          <t>23.38</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr"/>
@@ -6977,12 +7409,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>592885</t>
+          <t>668930</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Christian Yelich</t>
+          <t>Brice Turang</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -7007,14 +7439,26 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Drew Rasmussen</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>656876</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L7" t="n">
-        <v>46.2</v>
+        <v>45</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -7028,26 +7472,26 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
-        <v>38.2</v>
+        <v>36.6</v>
       </c>
       <c r="Q7" t="n">
-        <v>41.2</v>
+        <v>28.5</v>
       </c>
       <c r="R7" t="n">
         <v>27.6</v>
       </c>
       <c r="S7" t="n">
-        <v>92.09999999999999</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U7" t="n">
-        <v>25.3</v>
+        <v>65.2</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -7061,7 +7505,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -7086,7 +7530,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr"/>
@@ -7103,27 +7547,27 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/24, 1 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
@@ -7133,75 +7577,99 @@
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>9.81</t>
+          <t>7.79</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>43.95</t>
+          <t>43.34</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>89.29</t>
+          <t>90.54</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>100.9775</t>
+          <t>100.4264</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.4012</t>
+          <t>0.4283</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.1674</t>
+          <t>0.1712</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>0.3146</t>
+          <t>0.3413</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>73.16</t>
+          <t>70.25</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>32.25</t>
+          <t>13.2</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>34.24</t>
+          <t>28.21</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>19.09</t>
+          <t>23.43</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>17.1</t>
+          <t>20.1</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.1565</t>
-        </is>
-      </c>
-      <c r="BA7" t="inlineStr"/>
-      <c r="BB7" t="inlineStr"/>
-      <c r="BC7" t="inlineStr"/>
-      <c r="BD7" t="inlineStr"/>
-      <c r="BE7" t="inlineStr"/>
-      <c r="BF7" t="inlineStr"/>
+          <t>0.1715</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>6.02</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>36.65</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>88.92</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>0.3526</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>0.1222</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>23.38</t>
+        </is>
+      </c>
       <c r="BG7" t="inlineStr"/>
       <c r="BH7" t="inlineStr"/>
       <c r="BI7" t="inlineStr">
@@ -7217,12 +7685,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>668930</t>
+          <t>661388</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brice Turang</t>
+          <t>William Contreras</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -7247,14 +7715,26 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Drew Rasmussen</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>656876</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L8" t="n">
-        <v>46.2</v>
+        <v>43.1</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -7268,26 +7748,26 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P8" t="n">
-        <v>36.6</v>
+        <v>39.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>41.2</v>
+        <v>28.5</v>
       </c>
       <c r="R8" t="n">
         <v>27.6</v>
       </c>
       <c r="S8" t="n">
-        <v>81.90000000000001</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T8" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U8" t="n">
-        <v>65.2</v>
+        <v>37.8</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -7301,7 +7781,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -7326,7 +7806,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr"/>
@@ -7343,27 +7823,27 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
@@ -7373,12 +7853,12 @@
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>7.79</t>
+          <t>7.87</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>43.34</t>
+          <t>45.42</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
@@ -7388,60 +7868,84 @@
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>100.4264</t>
+          <t>101.6393</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.4283</t>
+          <t>0.4266</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.1712</t>
+          <t>0.1702</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.3413</t>
+          <t>0.3322</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>70.25</t>
+          <t>73.41</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>13.2</t>
+          <t>36.51</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>36.04</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>23.43</t>
+          <t>24.43</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>20.1</t>
+          <t>17.7</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.1715</t>
-        </is>
-      </c>
-      <c r="BA8" t="inlineStr"/>
-      <c r="BB8" t="inlineStr"/>
-      <c r="BC8" t="inlineStr"/>
-      <c r="BD8" t="inlineStr"/>
-      <c r="BE8" t="inlineStr"/>
-      <c r="BF8" t="inlineStr"/>
+          <t>0.1446</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>6.02</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>36.65</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>88.92</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>0.3526</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>0.1222</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>23.38</t>
+        </is>
+      </c>
       <c r="BG8" t="inlineStr"/>
       <c r="BH8" t="inlineStr"/>
       <c r="BI8" t="inlineStr">
@@ -7487,14 +7991,26 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Drew Rasmussen</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>656876</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L9" t="n">
-        <v>45.7</v>
+        <v>41.1</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -7508,23 +8024,23 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel</t>
+          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
         <v>47.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>41.2</v>
+        <v>28.5</v>
       </c>
       <c r="R9" t="n">
         <v>27.6</v>
       </c>
       <c r="S9" t="n">
-        <v>71.7</v>
+        <v>47.9</v>
       </c>
       <c r="T9" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U9" t="n">
         <v>13.3</v>
@@ -7541,7 +8057,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -7566,7 +8082,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr"/>
@@ -7603,7 +8119,7 @@
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -7676,12 +8192,36 @@
           <t>0.1342</t>
         </is>
       </c>
-      <c r="BA9" t="inlineStr"/>
-      <c r="BB9" t="inlineStr"/>
-      <c r="BC9" t="inlineStr"/>
-      <c r="BD9" t="inlineStr"/>
-      <c r="BE9" t="inlineStr"/>
-      <c r="BF9" t="inlineStr"/>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>6.02</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>36.65</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>88.92</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>0.3526</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>0.1222</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>23.38</t>
+        </is>
+      </c>
       <c r="BG9" t="inlineStr"/>
       <c r="BH9" t="inlineStr"/>
       <c r="BI9" t="inlineStr">
@@ -8249,24 +8789,24 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>806198</t>
+          <t>689414</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Cooper Pratt</t>
+          <t>Liam Hicks</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>2026-10-29T00:00:00Z</t>
@@ -8279,14 +8819,26 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Jacob Misiorowski</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>694819</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L12" t="n">
-        <v>32.5</v>
+        <v>32</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -8300,26 +8852,26 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>10.5</v>
+        <v>7.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>41.2</v>
+        <v>18.6</v>
       </c>
       <c r="R12" t="n">
         <v>27.6</v>
       </c>
       <c r="S12" t="n">
-        <v>59.8</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U12" t="n">
-        <v>24.9</v>
+        <v>19.5</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -8333,7 +8885,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -8358,7 +8910,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>H:2026 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD12" t="inlineStr"/>
@@ -8380,7 +8932,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -8390,12 +8942,12 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/21, 0 HR</t>
+          <t>Last 7 games: 6/24, 0 HR</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
@@ -8405,75 +8957,99 @@
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>3.67</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>27.28</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>84.6</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>96.5693</t>
+          <t>96.0847</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>0.3556</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>0.0997</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>0.3178</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>69.9</t>
+          <t>68.03</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>33.2</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>14.4</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>0.087</t>
-        </is>
-      </c>
-      <c r="BA12" t="inlineStr"/>
-      <c r="BB12" t="inlineStr"/>
-      <c r="BC12" t="inlineStr"/>
-      <c r="BD12" t="inlineStr"/>
-      <c r="BE12" t="inlineStr"/>
-      <c r="BF12" t="inlineStr"/>
+          <t>0.1347</t>
+        </is>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>4.89</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>34.56</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>87.74</t>
+        </is>
+      </c>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>0.2817</t>
+        </is>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>0.0996</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>25.57</t>
+        </is>
+      </c>
       <c r="BG12" t="inlineStr"/>
       <c r="BH12" t="inlineStr"/>
       <c r="BI12" t="inlineStr">
@@ -8489,12 +9065,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>689414</t>
+          <t>676356</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Liam Hicks</t>
+          <t>Jonny DeLuca</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -8519,7 +9095,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -8538,7 +9114,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>32</v>
+        <v>31.6</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -8552,11 +9128,11 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P13" t="n">
-        <v>7.8</v>
+        <v>10.6</v>
       </c>
       <c r="Q13" t="n">
         <v>18.6</v>
@@ -8565,13 +9141,13 @@
         <v>27.6</v>
       </c>
       <c r="S13" t="n">
-        <v>90.40000000000001</v>
+        <v>81.90000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U13" t="n">
-        <v>19.5</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -8585,7 +9161,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -8627,27 +9203,27 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 0 HR</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
@@ -8657,67 +9233,67 @@
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>3.67</t>
+          <t>3.21</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>27.28</t>
+          <t>30.68</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>84.6</t>
+          <t>85.74</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>96.0847</t>
+          <t>97.7063</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>0.3556</t>
+          <t>0.3262</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>0.0997</t>
+          <t>0.0879</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>0.3178</t>
+          <t>0.2628</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>68.03</t>
+          <t>72.75</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>28.1</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>41.33</t>
+          <t>45.6</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>24.29</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>14.4</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>0.1347</t>
+          <t>0.151</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
@@ -8765,24 +9341,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>676356</t>
+          <t>686217</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Jonny DeLuca</t>
+          <t>Sal Frelick</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>2026-10-29T00:00:00Z</t>
@@ -8795,17 +9371,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Jacob Misiorowski</t>
+          <t>Drew Rasmussen</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>694819</t>
+          <t>656876</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -8814,7 +9390,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>31.6</v>
+        <v>30.9</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -8828,26 +9404,26 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>10.6</v>
+        <v>5.4</v>
       </c>
       <c r="Q14" t="n">
-        <v>18.6</v>
+        <v>28.5</v>
       </c>
       <c r="R14" t="n">
         <v>27.6</v>
       </c>
       <c r="S14" t="n">
-        <v>81.90000000000001</v>
+        <v>71.7</v>
       </c>
       <c r="T14" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U14" t="n">
-        <v>70.59999999999999</v>
+        <v>17.3</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -8861,7 +9437,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -8903,27 +9479,27 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>17</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Last 7 games: 4/17, 0 HR</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
@@ -8933,97 +9509,97 @@
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>2.54</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>26.98</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>85.74</t>
+          <t>85.64</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>97.7063</t>
+          <t>96.2217</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.3262</t>
+          <t>0.3285</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>0.0879</t>
+          <t>0.0826</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>0.2628</t>
+          <t>0.2864</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
         <is>
-          <t>72.75</t>
+          <t>68.24</t>
         </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>28.1</t>
+          <t>3.76</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>45.6</t>
+          <t>39.46</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>20.9</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>6.4</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>0.0974</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>87.74</t>
+          <t>88.92</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>0.2817</t>
+          <t>0.3526</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
-          <t>0.0996</t>
+          <t>0.1222</t>
         </is>
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>25.57</t>
+          <t>23.38</t>
         </is>
       </c>
       <c r="BG14" t="inlineStr"/>
@@ -9350,11 +9926,23 @@
           <t>9</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Drew Rasmussen</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>656876</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L16" t="n">
-        <v>29.9</v>
+        <v>28.7</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -9368,14 +9956,14 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Projected Lineup, Platoon Edge</t>
         </is>
       </c>
       <c r="P16" t="n">
         <v>11.1</v>
       </c>
       <c r="Q16" t="n">
-        <v>41.2</v>
+        <v>28.5</v>
       </c>
       <c r="R16" t="n">
         <v>27.6</v>
@@ -9384,7 +9972,7 @@
         <v>40.2</v>
       </c>
       <c r="T16" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U16" t="n">
         <v>23.7</v>
@@ -9426,7 +10014,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr"/>
@@ -9463,7 +10051,7 @@
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -9536,12 +10124,36 @@
           <t>0.1042</t>
         </is>
       </c>
-      <c r="BA16" t="inlineStr"/>
-      <c r="BB16" t="inlineStr"/>
-      <c r="BC16" t="inlineStr"/>
-      <c r="BD16" t="inlineStr"/>
-      <c r="BE16" t="inlineStr"/>
-      <c r="BF16" t="inlineStr"/>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>6.02</t>
+        </is>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>36.65</t>
+        </is>
+      </c>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>88.92</t>
+        </is>
+      </c>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>0.3526</t>
+        </is>
+      </c>
+      <c r="BE16" t="inlineStr">
+        <is>
+          <t>0.1222</t>
+        </is>
+      </c>
+      <c r="BF16" t="inlineStr">
+        <is>
+          <t>23.38</t>
+        </is>
+      </c>
       <c r="BG16" t="inlineStr"/>
       <c r="BH16" t="inlineStr"/>
       <c r="BI16" t="inlineStr">
@@ -9557,12 +10169,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>686217</t>
+          <t>806198</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sal Frelick</t>
+          <t>Cooper Pratt</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -9587,14 +10199,26 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Drew Rasmussen</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>656876</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L17" t="n">
-        <v>28.8</v>
+        <v>28.6</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -9612,22 +10236,22 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>5.4</v>
+        <v>10.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>41.2</v>
+        <v>28.5</v>
       </c>
       <c r="R17" t="n">
         <v>27.6</v>
       </c>
       <c r="S17" t="n">
-        <v>47.9</v>
+        <v>59.8</v>
       </c>
       <c r="T17" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="U17" t="n">
-        <v>17.3</v>
+        <v>24.9</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -9641,7 +10265,7 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -9666,7 +10290,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr"/>
@@ -9683,12 +10307,12 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -9698,12 +10322,12 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Last 7 games: 4/17, 0 HR</t>
+          <t>Last 7 games: 6/21, 0 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -9713,75 +10337,99 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>26.98</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>85.64</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>96.2217</t>
+          <t>96.5693</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.3285</t>
+          <t>0.362</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.0826</t>
+          <t>0.096</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.2864</t>
+          <t>0.315</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>68.24</t>
+          <t>69.9</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>3.76</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>39.46</t>
+          <t>33.2</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>6.4</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.0974</t>
-        </is>
-      </c>
-      <c r="BA17" t="inlineStr"/>
-      <c r="BB17" t="inlineStr"/>
-      <c r="BC17" t="inlineStr"/>
-      <c r="BD17" t="inlineStr"/>
-      <c r="BE17" t="inlineStr"/>
-      <c r="BF17" t="inlineStr"/>
+          <t>0.087</t>
+        </is>
+      </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>6.02</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>36.65</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>88.92</t>
+        </is>
+      </c>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>0.3526</t>
+        </is>
+      </c>
+      <c r="BE17" t="inlineStr">
+        <is>
+          <t>0.1222</t>
+        </is>
+      </c>
+      <c r="BF17" t="inlineStr">
+        <is>
+          <t>23.38</t>
+        </is>
+      </c>
       <c r="BG17" t="inlineStr"/>
       <c r="BH17" t="inlineStr"/>
       <c r="BI17" t="inlineStr">

--- a/outputs/daily/hr_rankings_2026-10-28.xlsx
+++ b/outputs/daily/hr_rankings_2026-10-28.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -784,7 +784,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>52</v>
+        <v>54.5</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -808,10 +808,10 @@
         <v>28.5</v>
       </c>
       <c r="R2" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S2" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T2" t="n">
         <v>80</v>
@@ -821,39 +821,35 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -996,8 +992,16 @@
           <t>23.38</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI2" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -1036,7 +1040,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1060,7 +1064,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>48.3</v>
+        <v>50.8</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -1074,7 +1078,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -1084,10 +1088,10 @@
         <v>18.6</v>
       </c>
       <c r="R3" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S3" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T3" t="n">
         <v>50</v>
@@ -1097,39 +1101,35 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1272,8 +1272,16 @@
           <t>25.57</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI3" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -1312,7 +1320,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1336,7 +1344,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>47.6</v>
+        <v>50.1</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -1350,7 +1358,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -1360,10 +1368,10 @@
         <v>28.5</v>
       </c>
       <c r="R4" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S4" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T4" t="n">
         <v>50</v>
@@ -1373,39 +1381,35 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1548,8 +1552,16 @@
           <t>23.38</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI4" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -1588,7 +1600,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1612,7 +1624,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>46.7</v>
+        <v>49.2</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -1626,7 +1638,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -1636,10 +1648,10 @@
         <v>18.6</v>
       </c>
       <c r="R5" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S5" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T5" t="n">
         <v>80</v>
@@ -1649,39 +1661,35 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -1824,8 +1832,16 @@
           <t>25.57</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI5" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -1864,7 +1880,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1888,7 +1904,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>45</v>
+        <v>47.5</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -1902,7 +1918,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -1912,10 +1928,10 @@
         <v>28.5</v>
       </c>
       <c r="R6" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S6" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T6" t="n">
         <v>80</v>
@@ -1925,39 +1941,35 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2100,8 +2112,16 @@
           <t>23.38</t>
         </is>
       </c>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI6" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -2140,7 +2160,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -2164,7 +2184,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>45</v>
+        <v>47.5</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -2178,7 +2198,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -2188,10 +2208,10 @@
         <v>28.5</v>
       </c>
       <c r="R7" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S7" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T7" t="n">
         <v>80</v>
@@ -2201,39 +2221,35 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2376,8 +2392,16 @@
           <t>23.38</t>
         </is>
       </c>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI7" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -2416,7 +2440,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -2440,7 +2464,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>43.1</v>
+        <v>45.6</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -2454,7 +2478,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -2464,10 +2488,10 @@
         <v>28.5</v>
       </c>
       <c r="R8" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S8" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T8" t="n">
         <v>50</v>
@@ -2477,39 +2501,35 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2652,8 +2672,16 @@
           <t>23.38</t>
         </is>
       </c>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI8" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -2692,7 +2720,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -2716,7 +2744,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>41.1</v>
+        <v>43.6</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -2730,7 +2758,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -2740,10 +2768,10 @@
         <v>28.5</v>
       </c>
       <c r="R9" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S9" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T9" t="n">
         <v>80</v>
@@ -2753,39 +2781,35 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -2928,8 +2952,16 @@
           <t>23.38</t>
         </is>
       </c>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI9" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -2948,7 +2980,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yandy Diaz</t>
+          <t>Yandy Díaz</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2968,7 +3000,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -2992,7 +3024,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>40.1</v>
+        <v>42.6</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -3006,7 +3038,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -3016,10 +3048,10 @@
         <v>18.6</v>
       </c>
       <c r="R10" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S10" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T10" t="n">
         <v>50</v>
@@ -3029,39 +3061,35 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3204,8 +3232,16 @@
           <t>25.57</t>
         </is>
       </c>
-      <c r="BG10" t="inlineStr"/>
-      <c r="BH10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI10" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -3219,12 +3255,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>683748</t>
+          <t>668723</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Victor Mesa</t>
+          <t>Ryan Vilade</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -3244,7 +3280,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3268,7 +3304,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>39.6</v>
+        <v>36.6</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -3282,62 +3318,58 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>43.6</v>
+        <v>43.3</v>
       </c>
       <c r="Q11" t="n">
         <v>18.6</v>
       </c>
       <c r="R11" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S11" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T11" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U11" t="n">
-        <v>54.9</v>
+        <v>0</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3357,27 +3389,27 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Contact streak: 8/22 over last 7 games</t>
+          <t>Last 7 games: 2/21, 0 HR</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -3387,67 +3419,67 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>8.72</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>42.41</t>
+          <t>50.43</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>89.91</t>
+          <t>91.42</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>100.2811</t>
+          <t>102.6273</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.4339</t>
+          <t>0.3949</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.1893</t>
+          <t>0.1562</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3305</t>
+          <t>0.3174</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>73.58</t>
+          <t>75.84</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>32.32</t>
+          <t>58.84</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>40.38</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>33.35</t>
+          <t>23.91</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.2134</t>
+          <t>0.1288</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
@@ -3480,8 +3512,16 @@
           <t>25.57</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI11" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -3520,7 +3560,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -3544,7 +3584,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>32</v>
+        <v>34.5</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -3558,7 +3598,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -3568,10 +3608,10 @@
         <v>18.6</v>
       </c>
       <c r="R12" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S12" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T12" t="n">
         <v>80</v>
@@ -3581,39 +3621,35 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -3756,8 +3792,16 @@
           <t>25.57</t>
         </is>
       </c>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI12" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -3796,7 +3840,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -3820,7 +3864,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>31.6</v>
+        <v>34.1</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -3834,7 +3878,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Hot Hitter/Streak</t>
+          <t>Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -3844,10 +3888,10 @@
         <v>18.6</v>
       </c>
       <c r="R13" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S13" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T13" t="n">
         <v>50</v>
@@ -3857,39 +3901,35 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4032,8 +4072,16 @@
           <t>25.57</t>
         </is>
       </c>
-      <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI13" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -4072,7 +4120,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -4096,7 +4144,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>30.9</v>
+        <v>33.4</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -4110,7 +4158,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -4120,10 +4168,10 @@
         <v>28.5</v>
       </c>
       <c r="R14" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S14" t="n">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="T14" t="n">
         <v>80</v>
@@ -4133,39 +4181,35 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4308,8 +4352,16 @@
           <t>23.38</t>
         </is>
       </c>
-      <c r="BG14" t="inlineStr"/>
-      <c r="BH14" t="inlineStr"/>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI14" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -4323,24 +4375,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>680700</t>
+          <t>666152</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Richie Palacios</t>
+          <t>David Hamilton</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>2026-10-29T00:00:00Z</t>
@@ -4348,22 +4400,22 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Jacob Misiorowski</t>
+          <t>Drew Rasmussen</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>694819</t>
+          <t>656876</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -4372,7 +4424,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>30.2</v>
+        <v>31.2</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -4386,62 +4438,58 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>15.4</v>
+        <v>11.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>18.6</v>
+        <v>28.5</v>
       </c>
       <c r="R15" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S15" t="n">
-        <v>59.8</v>
+        <v>44.8</v>
       </c>
       <c r="T15" t="n">
         <v>80</v>
       </c>
       <c r="U15" t="n">
-        <v>19.5</v>
+        <v>23.7</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -4466,7 +4514,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -4476,12 +4524,12 @@
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/20, 0 HR</t>
+          <t>Last 7 games: 5/18, 0 HR</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -4491,101 +4539,109 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>27.87</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>87.31</t>
+          <t>86.74</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>97.1084</t>
+          <t>96.8019</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.3655</t>
+          <t>0.3169</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.1018</t>
+          <t>0.0967</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3213</t>
+          <t>0.2712</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>68.91</t>
+          <t>69.66</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>37.09</t>
+          <t>35.88</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>20.98</t>
+          <t>24.48</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>0.1042</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>87.74</t>
+          <t>88.92</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>0.2817</t>
+          <t>0.3526</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>0.0996</t>
+          <t>0.1222</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>25.57</t>
-        </is>
-      </c>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
+          <t>23.38</t>
+        </is>
+      </c>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI15" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -4599,12 +4655,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>666152</t>
+          <t>806198</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>David Hamilton</t>
+          <t>Cooper Pratt</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -4624,12 +4680,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -4648,7 +4704,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>28.7</v>
+        <v>31.1</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -4662,65 +4718,61 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>11.1</v>
+        <v>10.5</v>
       </c>
       <c r="Q16" t="n">
         <v>28.5</v>
       </c>
       <c r="R16" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S16" t="n">
-        <v>40.2</v>
+        <v>64.3</v>
       </c>
       <c r="T16" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U16" t="n">
-        <v>23.7</v>
+        <v>24.9</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr"/>
@@ -4737,12 +4789,12 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -4752,12 +4804,12 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/18, 0 HR</t>
+          <t>Last 7 games: 6/21, 0 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -4767,67 +4819,67 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>27.87</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>86.74</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>96.8019</t>
+          <t>96.5693</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.3169</t>
+          <t>0.362</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.0967</t>
+          <t>0.096</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.2712</t>
+          <t>0.315</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>69.66</t>
+          <t>69.9</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>6.52</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>35.88</t>
+          <t>33.2</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>24.48</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.1042</t>
+          <t>0.087</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
@@ -4860,8 +4912,16 @@
           <t>23.38</t>
         </is>
       </c>
-      <c r="BG16" t="inlineStr"/>
-      <c r="BH16" t="inlineStr"/>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI16" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -4875,24 +4935,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>806198</t>
+          <t>802415</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cooper Pratt</t>
+          <t>Chandler Simpson</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>2026-10-29T00:00:00Z</t>
@@ -4900,22 +4960,22 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Drew Rasmussen</t>
+          <t>Jacob Misiorowski</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>656876</t>
+          <t>694819</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -4924,7 +4984,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>28.6</v>
+        <v>29.2</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -4938,65 +4998,61 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>10.5</v>
+        <v>0.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>28.5</v>
+        <v>18.6</v>
       </c>
       <c r="R17" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S17" t="n">
-        <v>59.8</v>
+        <v>76.2</v>
       </c>
       <c r="T17" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U17" t="n">
-        <v>24.9</v>
+        <v>15.3</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr"/>
@@ -5018,7 +5074,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -5028,12 +5084,12 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/21, 0 HR</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -5043,101 +5099,109 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>83.88</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>96.5693</t>
+          <t>92.929</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>0.3087</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>0.0382</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>0.2732</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>69.9</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>33.2</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>12.51</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>88.92</t>
+          <t>87.74</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>0.3526</t>
+          <t>0.2817</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>0.1222</t>
+          <t>0.0996</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>23.38</t>
-        </is>
-      </c>
-      <c r="BG17" t="inlineStr"/>
-      <c r="BH17" t="inlineStr"/>
+          <t>25.57</t>
+        </is>
+      </c>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI17" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -5151,12 +5215,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>802415</t>
+          <t>810938</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chandler Simpson</t>
+          <t>Ben Williamson</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -5176,12 +5240,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -5200,7 +5264,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>26.7</v>
+        <v>27.8</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -5214,62 +5278,58 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0.2</v>
+        <v>11.6</v>
       </c>
       <c r="Q18" t="n">
         <v>18.6</v>
       </c>
       <c r="R18" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S18" t="n">
-        <v>71.7</v>
+        <v>64.3</v>
       </c>
       <c r="T18" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U18" t="n">
-        <v>15.3</v>
+        <v>0</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5289,12 +5349,12 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -5304,12 +5364,12 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 0 HR</t>
+          <t>Last 7 games: 2/19, 0 HR</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -5319,67 +5379,67 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>35.39</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>83.88</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>92.929</t>
+          <t>98.4446</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.3087</t>
+          <t>0.3241</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.0382</t>
+          <t>0.0789</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.2732</t>
+          <t>0.2809</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>69.49</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>27.55</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>12.51</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.0731</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
@@ -5412,8 +5472,16 @@
           <t>25.57</t>
         </is>
       </c>
-      <c r="BG18" t="inlineStr"/>
-      <c r="BH18" t="inlineStr"/>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI18" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -5452,7 +5520,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -5476,7 +5544,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>23.9</v>
+        <v>26.4</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -5490,7 +5558,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -5500,10 +5568,10 @@
         <v>17.3</v>
       </c>
       <c r="R19" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T19" t="n">
         <v>75</v>
@@ -5513,39 +5581,35 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -5688,8 +5752,16 @@
           <t>25.57</t>
         </is>
       </c>
-      <c r="BG19" t="inlineStr"/>
-      <c r="BH19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI19" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -6054,7 +6126,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -6078,7 +6150,7 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>52</v>
+        <v>54.5</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
@@ -6092,7 +6164,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -6102,10 +6174,10 @@
         <v>28.5</v>
       </c>
       <c r="R2" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S2" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T2" t="n">
         <v>80</v>
@@ -6115,39 +6187,35 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6290,8 +6358,16 @@
           <t>23.38</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI2" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -6330,7 +6406,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -6354,7 +6430,7 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>48.3</v>
+        <v>50.8</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -6368,7 +6444,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -6378,10 +6454,10 @@
         <v>18.6</v>
       </c>
       <c r="R3" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S3" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T3" t="n">
         <v>50</v>
@@ -6391,39 +6467,35 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6566,8 +6638,16 @@
           <t>25.57</t>
         </is>
       </c>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI3" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -6606,7 +6686,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -6630,7 +6710,7 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>47.6</v>
+        <v>50.1</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -6644,7 +6724,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot</t>
+          <t>Strong Barrel, Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P4" t="n">
@@ -6654,10 +6734,10 @@
         <v>28.5</v>
       </c>
       <c r="R4" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S4" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T4" t="n">
         <v>50</v>
@@ -6667,39 +6747,35 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -6842,8 +6918,16 @@
           <t>23.38</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr"/>
-      <c r="BH4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI4" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -6882,7 +6966,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -6906,7 +6990,7 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>46.7</v>
+        <v>49.2</v>
       </c>
       <c r="M5" t="inlineStr">
         <is>
@@ -6920,7 +7004,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P5" t="n">
@@ -6930,10 +7014,10 @@
         <v>18.6</v>
       </c>
       <c r="R5" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S5" t="n">
-        <v>95.5</v>
+        <v>100</v>
       </c>
       <c r="T5" t="n">
         <v>80</v>
@@ -6943,39 +7027,35 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7118,8 +7198,16 @@
           <t>25.57</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI5" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -7158,7 +7246,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -7182,7 +7270,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>45</v>
+        <v>47.5</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
@@ -7196,7 +7284,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P6" t="n">
@@ -7206,10 +7294,10 @@
         <v>28.5</v>
       </c>
       <c r="R6" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S6" t="n">
-        <v>92.09999999999999</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="T6" t="n">
         <v>80</v>
@@ -7219,39 +7307,35 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
       <c r="AC6" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7394,8 +7478,16 @@
           <t>23.38</t>
         </is>
       </c>
-      <c r="BG6" t="inlineStr"/>
-      <c r="BH6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI6" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -7434,7 +7526,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -7458,7 +7550,7 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>45</v>
+        <v>47.5</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -7472,7 +7564,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P7" t="n">
@@ -7482,10 +7574,10 @@
         <v>28.5</v>
       </c>
       <c r="R7" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S7" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T7" t="n">
         <v>80</v>
@@ -7495,39 +7587,35 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr"/>
       <c r="AC7" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7670,8 +7758,16 @@
           <t>23.38</t>
         </is>
       </c>
-      <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr"/>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI7" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -7710,7 +7806,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -7734,7 +7830,7 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>43.1</v>
+        <v>45.6</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -7748,7 +7844,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P8" t="n">
@@ -7758,10 +7854,10 @@
         <v>28.5</v>
       </c>
       <c r="R8" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S8" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T8" t="n">
         <v>50</v>
@@ -7771,39 +7867,35 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr"/>
       <c r="AC8" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -7946,8 +8038,16 @@
           <t>23.38</t>
         </is>
       </c>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI8" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -7986,7 +8086,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -8010,7 +8110,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>41.1</v>
+        <v>43.6</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -8024,7 +8124,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Platoon Edge</t>
+          <t>Strong Barrel, Platoon Edge</t>
         </is>
       </c>
       <c r="P9" t="n">
@@ -8034,10 +8134,10 @@
         <v>28.5</v>
       </c>
       <c r="R9" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S9" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T9" t="n">
         <v>80</v>
@@ -8047,39 +8147,35 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr"/>
       <c r="AC9" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8222,8 +8318,16 @@
           <t>23.38</t>
         </is>
       </c>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI9" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -8242,7 +8346,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yandy Diaz</t>
+          <t>Yandy Díaz</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -8262,7 +8366,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -8286,7 +8390,7 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>40.1</v>
+        <v>42.6</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -8300,7 +8404,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot</t>
+          <t>Premium Lineup Spot</t>
         </is>
       </c>
       <c r="P10" t="n">
@@ -8310,10 +8414,10 @@
         <v>18.6</v>
       </c>
       <c r="R10" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S10" t="n">
-        <v>88.7</v>
+        <v>93.2</v>
       </c>
       <c r="T10" t="n">
         <v>50</v>
@@ -8323,39 +8427,35 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr"/>
       <c r="AC10" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8498,8 +8598,16 @@
           <t>25.57</t>
         </is>
       </c>
-      <c r="BG10" t="inlineStr"/>
-      <c r="BH10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI10" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -8513,12 +8621,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>683748</t>
+          <t>668723</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Victor Mesa</t>
+          <t>Ryan Vilade</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -8538,7 +8646,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -8562,7 +8670,7 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>39.6</v>
+        <v>36.6</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -8576,62 +8684,58 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>43.6</v>
+        <v>43.3</v>
       </c>
       <c r="Q11" t="n">
         <v>18.6</v>
       </c>
       <c r="R11" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S11" t="n">
-        <v>47.9</v>
+        <v>52.4</v>
       </c>
       <c r="T11" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U11" t="n">
-        <v>54.9</v>
+        <v>0</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr"/>
       <c r="AC11" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -8651,27 +8755,27 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Contact streak: 8/22 over last 7 games</t>
+          <t>Last 7 games: 2/21, 0 HR</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
@@ -8681,67 +8785,67 @@
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>8.72</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>42.41</t>
+          <t>50.43</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>89.91</t>
+          <t>91.42</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>100.2811</t>
+          <t>102.6273</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.4339</t>
+          <t>0.3949</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.1893</t>
+          <t>0.1562</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>0.3305</t>
+          <t>0.3174</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>73.58</t>
+          <t>75.84</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>32.32</t>
+          <t>58.84</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>40.38</t>
+          <t>24.71</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>33.35</t>
+          <t>23.91</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>10.1</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.2134</t>
+          <t>0.1288</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
@@ -8774,8 +8878,16 @@
           <t>25.57</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr"/>
-      <c r="BH11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI11" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -8814,7 +8926,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -8838,7 +8950,7 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>32</v>
+        <v>34.5</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -8852,7 +8964,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Projected Lineup, Premium Lineup Spot, Platoon Edge</t>
+          <t>Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P12" t="n">
@@ -8862,10 +8974,10 @@
         <v>18.6</v>
       </c>
       <c r="R12" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S12" t="n">
-        <v>90.40000000000001</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="T12" t="n">
         <v>80</v>
@@ -8875,39 +8987,35 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr"/>
       <c r="AC12" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9050,8 +9158,16 @@
           <t>25.57</t>
         </is>
       </c>
-      <c r="BG12" t="inlineStr"/>
-      <c r="BH12" t="inlineStr"/>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI12" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -9090,7 +9206,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -9114,7 +9230,7 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>31.6</v>
+        <v>34.1</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -9128,7 +9244,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>Projected Lineup, Hot Hitter/Streak</t>
+          <t>Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P13" t="n">
@@ -9138,10 +9254,10 @@
         <v>18.6</v>
       </c>
       <c r="R13" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S13" t="n">
-        <v>81.90000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="T13" t="n">
         <v>50</v>
@@ -9151,39 +9267,35 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr"/>
       <c r="AC13" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9326,8 +9438,16 @@
           <t>25.57</t>
         </is>
       </c>
-      <c r="BG13" t="inlineStr"/>
-      <c r="BH13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI13" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -9366,7 +9486,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -9390,7 +9510,7 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>30.9</v>
+        <v>33.4</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -9404,7 +9524,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P14" t="n">
@@ -9414,10 +9534,10 @@
         <v>28.5</v>
       </c>
       <c r="R14" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S14" t="n">
-        <v>71.7</v>
+        <v>76.2</v>
       </c>
       <c r="T14" t="n">
         <v>80</v>
@@ -9427,39 +9547,35 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr"/>
       <c r="AC14" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9602,8 +9718,16 @@
           <t>23.38</t>
         </is>
       </c>
-      <c r="BG14" t="inlineStr"/>
-      <c r="BH14" t="inlineStr"/>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI14" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -9617,24 +9741,24 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>680700</t>
+          <t>666152</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Richie Palacios</t>
+          <t>David Hamilton</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>MIL</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>TB</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>2026-10-29T00:00:00Z</t>
@@ -9642,22 +9766,22 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Jacob Misiorowski</t>
+          <t>Drew Rasmussen</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>694819</t>
+          <t>656876</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -9666,7 +9790,7 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>30.2</v>
+        <v>31.2</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
@@ -9680,62 +9804,58 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>15.4</v>
+        <v>11.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>18.6</v>
+        <v>28.5</v>
       </c>
       <c r="R15" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S15" t="n">
-        <v>59.8</v>
+        <v>44.8</v>
       </c>
       <c r="T15" t="n">
         <v>80</v>
       </c>
       <c r="U15" t="n">
-        <v>19.5</v>
+        <v>23.7</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr"/>
       <c r="AC15" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -9760,7 +9880,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
@@ -9770,12 +9890,12 @@
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/20, 0 HR</t>
+          <t>Last 7 games: 5/18, 0 HR</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
@@ -9785,101 +9905,109 @@
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>4.57</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>27.87</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>87.31</t>
+          <t>86.74</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>97.1084</t>
+          <t>96.8019</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.3655</t>
+          <t>0.3169</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>0.1018</t>
+          <t>0.0967</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>0.3213</t>
+          <t>0.2712</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
         <is>
-          <t>68.91</t>
+          <t>69.66</t>
         </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>3.94</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>37.09</t>
+          <t>35.88</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>20.98</t>
+          <t>24.48</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>7.3</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>0.1042</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>34.56</t>
+          <t>36.65</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>87.74</t>
+          <t>88.92</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>0.2817</t>
+          <t>0.3526</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
-          <t>0.0996</t>
+          <t>0.1222</t>
         </is>
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>25.57</t>
-        </is>
-      </c>
-      <c r="BG15" t="inlineStr"/>
-      <c r="BH15" t="inlineStr"/>
+          <t>23.38</t>
+        </is>
+      </c>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI15" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -9893,12 +10021,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>666152</t>
+          <t>806198</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>David Hamilton</t>
+          <t>Cooper Pratt</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -9918,12 +10046,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -9942,7 +10070,7 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>28.7</v>
+        <v>31.1</v>
       </c>
       <c r="M16" t="inlineStr">
         <is>
@@ -9956,65 +10084,61 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P16" t="n">
-        <v>11.1</v>
+        <v>10.5</v>
       </c>
       <c r="Q16" t="n">
         <v>28.5</v>
       </c>
       <c r="R16" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S16" t="n">
-        <v>40.2</v>
+        <v>64.3</v>
       </c>
       <c r="T16" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U16" t="n">
-        <v>23.7</v>
+        <v>24.9</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr"/>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026 P:2026/2025</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr"/>
@@ -10031,12 +10155,12 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -10046,12 +10170,12 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>Last 7 games: 5/18, 0 HR</t>
+          <t>Last 7 games: 6/21, 0 HR</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
@@ -10061,67 +10185,67 @@
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>27.87</t>
+          <t>27.4</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>86.74</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>96.8019</t>
+          <t>96.5693</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.3169</t>
+          <t>0.362</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>0.0967</t>
+          <t>0.096</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>0.2712</t>
+          <t>0.315</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
         <is>
-          <t>69.66</t>
+          <t>69.9</t>
         </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>6.52</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>35.88</t>
+          <t>33.2</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>24.48</t>
+          <t>21.1</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>0.1042</t>
+          <t>0.087</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
@@ -10154,8 +10278,16 @@
           <t>23.38</t>
         </is>
       </c>
-      <c r="BG16" t="inlineStr"/>
-      <c r="BH16" t="inlineStr"/>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI16" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -10169,24 +10301,24 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>806198</t>
+          <t>802415</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cooper Pratt</t>
+          <t>Chandler Simpson</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>TB</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>MIL</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>TB</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>2026-10-29T00:00:00Z</t>
@@ -10194,22 +10326,22 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Drew Rasmussen</t>
+          <t>Jacob Misiorowski</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>656876</t>
+          <t>694819</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -10218,7 +10350,7 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>28.6</v>
+        <v>29.2</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
@@ -10232,65 +10364,61 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Projected Lineup</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>10.5</v>
+        <v>0.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>28.5</v>
+        <v>18.6</v>
       </c>
       <c r="R17" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S17" t="n">
-        <v>59.8</v>
+        <v>76.2</v>
       </c>
       <c r="T17" t="n">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="U17" t="n">
-        <v>24.9</v>
+        <v>15.3</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr"/>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>H:2026 P:2026/2025</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AD17" t="inlineStr"/>
@@ -10312,7 +10440,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>27</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
@@ -10322,12 +10450,12 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/21, 0 HR</t>
+          <t>Last 7 games: 6/27, 0 HR</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>same-side matchup; pitcher baseline 6.0% barrel, 15.2 HR allowed</t>
+          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
@@ -10337,101 +10465,109 @@
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>27.4</t>
+          <t>14.71</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>83.88</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>96.5693</t>
+          <t>92.929</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>0.3087</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>0.0382</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>0.2732</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
         <is>
-          <t>69.9</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>33.2</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>12.51</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>36.65</t>
+          <t>34.56</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>88.92</t>
+          <t>87.74</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>0.3526</t>
+          <t>0.2817</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
-          <t>0.1222</t>
+          <t>0.0996</t>
         </is>
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>23.38</t>
-        </is>
-      </c>
-      <c r="BG17" t="inlineStr"/>
-      <c r="BH17" t="inlineStr"/>
+          <t>25.57</t>
+        </is>
+      </c>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI17" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -10445,12 +10581,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>802415</t>
+          <t>810938</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Chandler Simpson</t>
+          <t>Ben Williamson</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -10470,12 +10606,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -10494,7 +10630,7 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>26.7</v>
+        <v>27.8</v>
       </c>
       <c r="M18" t="inlineStr">
         <is>
@@ -10508,62 +10644,58 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>No major boost</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0.2</v>
+        <v>11.6</v>
       </c>
       <c r="Q18" t="n">
         <v>18.6</v>
       </c>
       <c r="R18" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S18" t="n">
-        <v>71.7</v>
+        <v>64.3</v>
       </c>
       <c r="T18" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U18" t="n">
-        <v>15.3</v>
+        <v>0</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr"/>
       <c r="AC18" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10583,12 +10715,12 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
@@ -10598,12 +10730,12 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/27, 0 HR</t>
+          <t>Last 7 games: 2/19, 0 HR</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 4.9% barrel, 12.2 HR allowed</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -10613,67 +10745,67 @@
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>14.71</t>
+          <t>35.39</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>83.88</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>92.929</t>
+          <t>98.4446</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.3087</t>
+          <t>0.3241</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
         <is>
-          <t>0.0382</t>
+          <t>0.0789</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>0.2732</t>
+          <t>0.2809</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>69.49</t>
         </is>
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>10.53</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>27.55</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>12.51</t>
+          <t>14.95</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.0731</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
@@ -10706,8 +10838,16 @@
           <t>25.57</t>
         </is>
       </c>
-      <c r="BG18" t="inlineStr"/>
-      <c r="BH18" t="inlineStr"/>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI18" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
@@ -10746,7 +10886,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Pre-Game</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -10770,7 +10910,7 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>23.9</v>
+        <v>26.4</v>
       </c>
       <c r="M19" t="inlineStr">
         <is>
@@ -10784,7 +10924,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Projected Lineup, Platoon Edge</t>
+          <t>Platoon Edge</t>
         </is>
       </c>
       <c r="P19" t="n">
@@ -10794,10 +10934,10 @@
         <v>17.3</v>
       </c>
       <c r="R19" t="n">
-        <v>27.6</v>
+        <v>40.1</v>
       </c>
       <c r="S19" t="n">
-        <v>40.2</v>
+        <v>44.8</v>
       </c>
       <c r="T19" t="n">
         <v>75</v>
@@ -10807,39 +10947,35 @@
       </c>
       <c r="V19" t="inlineStr">
         <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>RotoWire projected lineup; MLB probable pitchers</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>lineup projected / unconfirmed</t>
-        </is>
-      </c>
+          <t>MLB Stats API; RotoWire</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr"/>
       <c r="AC19" t="inlineStr">
         <is>
           <t>H:2026/2025 P:2026/2025</t>
@@ -10982,8 +11118,16 @@
           <t>25.57</t>
         </is>
       </c>
-      <c r="BG19" t="inlineStr"/>
-      <c r="BH19" t="inlineStr"/>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="BI19" t="inlineStr">
         <is>
           <t>Tropicana Field</t>
